--- a/Descuentos/Productos_backup.xlsx
+++ b/Descuentos/Productos_backup.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Stock" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stock" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -681,7 +681,7 @@
         </is>
       </c>
       <c r="C24" s="2" t="n">
-        <v>-24</v>
+        <v>-72</v>
       </c>
     </row>
     <row r="25">
@@ -694,7 +694,7 @@
         </is>
       </c>
       <c r="C25" s="2" t="n">
-        <v>-24</v>
+        <v>-72</v>
       </c>
     </row>
     <row r="26">
@@ -740,7 +740,7 @@
         </is>
       </c>
       <c r="C29" s="2" t="n">
-        <v>-12</v>
+        <v>-36</v>
       </c>
     </row>
     <row r="30">
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="C37" s="2" t="n">
-        <v>-2</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="38">
@@ -898,7 +898,7 @@
         </is>
       </c>
       <c r="C43" s="2" t="n">
-        <v>-2</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="44">
@@ -1439,7 +1439,7 @@
         </is>
       </c>
       <c r="C92" s="2" t="n">
-        <v>-72</v>
+        <v>-216</v>
       </c>
     </row>
     <row r="93">
@@ -2013,7 +2013,7 @@
         </is>
       </c>
       <c r="C144" s="2" t="n">
-        <v>-28</v>
+        <v>-84</v>
       </c>
     </row>
     <row r="145">
@@ -2257,7 +2257,7 @@
         </is>
       </c>
       <c r="C166" s="2" t="n">
-        <v>-24</v>
+        <v>-72</v>
       </c>
     </row>
     <row r="167">
@@ -2380,7 +2380,7 @@
         </is>
       </c>
       <c r="C177" s="2" t="n">
-        <v>-20</v>
+        <v>-60</v>
       </c>
     </row>
     <row r="178">
@@ -2470,7 +2470,7 @@
         </is>
       </c>
       <c r="C185" s="2" t="n">
-        <v>-20</v>
+        <v>-60</v>
       </c>
     </row>
     <row r="186">
@@ -2560,7 +2560,7 @@
         </is>
       </c>
       <c r="C193" s="2" t="n">
-        <v>-40</v>
+        <v>-120</v>
       </c>
     </row>
     <row r="194">
@@ -2661,7 +2661,7 @@
         </is>
       </c>
       <c r="C202" s="2" t="n">
-        <v>-40</v>
+        <v>-120</v>
       </c>
     </row>
     <row r="203">
@@ -3026,7 +3026,7 @@
         </is>
       </c>
       <c r="C235" s="2" t="n">
-        <v>-2</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="236">
@@ -3039,7 +3039,7 @@
         </is>
       </c>
       <c r="C236" s="2" t="n">
-        <v>-14</v>
+        <v>-42</v>
       </c>
     </row>
     <row r="237">

--- a/Descuentos/Productos_backup.xlsx
+++ b/Descuentos/Productos_backup.xlsx
@@ -889,13 +889,13 @@
         </is>
       </c>
       <c r="D5" s="42" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E5" s="42" t="n">
         <v>-2</v>
       </c>
       <c r="F5" s="43" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="G5" s="38" t="n"/>
       <c r="H5" s="38" t="n"/>
@@ -925,13 +925,13 @@
         </is>
       </c>
       <c r="D6" s="42" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E6" s="42" t="n">
         <v>-1</v>
       </c>
       <c r="F6" s="43" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G6" s="38" t="n"/>
       <c r="H6" s="38" t="n"/>
@@ -1081,13 +1081,13 @@
         </is>
       </c>
       <c r="D11" s="42" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E11" s="42" t="n">
         <v>-1</v>
       </c>
       <c r="F11" s="43" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G11" s="38" t="n"/>
       <c r="H11" s="38" t="n"/>
@@ -1233,13 +1233,13 @@
         </is>
       </c>
       <c r="D16" s="42" t="n">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E16" s="42" t="n">
         <v>-1</v>
       </c>
       <c r="F16" s="43" t="n">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="G16" s="38" t="n"/>
       <c r="H16" s="38" t="n"/>
@@ -1269,13 +1269,13 @@
         </is>
       </c>
       <c r="D17" s="42" t="n">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E17" s="42" t="n">
         <v>-1</v>
       </c>
       <c r="F17" s="43" t="n">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="G17" s="38" t="n"/>
       <c r="H17" s="38" t="n"/>
@@ -1305,13 +1305,13 @@
         </is>
       </c>
       <c r="D18" s="42" t="n">
-        <v>260</v>
+        <v>252</v>
       </c>
       <c r="E18" s="42" t="n">
         <v>-8</v>
       </c>
       <c r="F18" s="43" t="n">
-        <v>252</v>
+        <v>244</v>
       </c>
       <c r="G18" s="38" t="n"/>
       <c r="H18" s="38" t="n"/>
@@ -1341,13 +1341,13 @@
         </is>
       </c>
       <c r="D19" s="42" t="n">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E19" s="42" t="n">
         <v>-1</v>
       </c>
       <c r="F19" s="43" t="n">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="G19" s="38" t="n"/>
       <c r="H19" s="38" t="n"/>
@@ -1441,13 +1441,13 @@
         </is>
       </c>
       <c r="D22" s="42" t="n">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E22" s="42" t="n">
         <v>-1</v>
       </c>
       <c r="F22" s="43" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G22" s="38" t="n"/>
       <c r="H22" s="38" t="n"/>
@@ -1589,13 +1589,13 @@
         </is>
       </c>
       <c r="D27" s="42" t="n">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="E27" s="42" t="n">
         <v>-2</v>
       </c>
       <c r="F27" s="43" t="n">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="G27" s="38" t="n"/>
       <c r="H27" s="38" t="n"/>
@@ -1753,13 +1753,13 @@
         </is>
       </c>
       <c r="D32" s="42" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E32" s="42" t="n">
         <v>-2</v>
       </c>
       <c r="F32" s="43" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G32" s="38" t="n"/>
       <c r="H32" s="38" t="n"/>
@@ -1789,13 +1789,13 @@
         </is>
       </c>
       <c r="D33" s="42" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E33" s="42" t="n">
         <v>-3</v>
       </c>
       <c r="F33" s="43" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G33" s="38" t="n"/>
       <c r="H33" s="38" t="n"/>
@@ -1825,13 +1825,13 @@
         </is>
       </c>
       <c r="D34" s="42" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E34" s="42" t="n">
         <v>-1</v>
       </c>
       <c r="F34" s="43" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G34" s="38" t="n"/>
       <c r="H34" s="38" t="n"/>
@@ -1893,13 +1893,13 @@
         </is>
       </c>
       <c r="D36" s="42" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E36" s="42" t="n">
         <v>-1</v>
       </c>
       <c r="F36" s="43" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G36" s="38" t="n"/>
       <c r="H36" s="38" t="n"/>
@@ -1929,13 +1929,13 @@
         </is>
       </c>
       <c r="D37" s="42" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E37" s="42" t="n">
         <v>-1</v>
       </c>
       <c r="F37" s="43" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G37" s="38" t="n"/>
       <c r="H37" s="38" t="n"/>
@@ -2061,13 +2061,13 @@
         </is>
       </c>
       <c r="D41" s="42" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E41" s="42" t="n">
         <v>-1</v>
       </c>
       <c r="F41" s="43" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G41" s="38" t="n"/>
       <c r="H41" s="38" t="n"/>
@@ -2097,13 +2097,13 @@
         </is>
       </c>
       <c r="D42" s="42" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="E42" s="42" t="n">
         <v>-1</v>
       </c>
       <c r="F42" s="43" t="n">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="G42" s="38" t="n"/>
       <c r="H42" s="38" t="n"/>
@@ -2161,13 +2161,13 @@
         </is>
       </c>
       <c r="D44" s="42" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E44" s="42" t="n">
         <v>-1</v>
       </c>
       <c r="F44" s="43" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G44" s="38" t="n"/>
       <c r="H44" s="38" t="n"/>
@@ -2197,13 +2197,13 @@
         </is>
       </c>
       <c r="D45" s="42" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E45" s="42" t="n">
         <v>-1</v>
       </c>
       <c r="F45" s="43" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G45" s="38" t="n"/>
       <c r="H45" s="38" t="n"/>
@@ -2233,13 +2233,13 @@
         </is>
       </c>
       <c r="D46" s="42" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E46" s="42" t="n">
         <v>-1</v>
       </c>
       <c r="F46" s="43" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G46" s="38" t="n"/>
       <c r="H46" s="38" t="n"/>
@@ -2301,13 +2301,13 @@
         </is>
       </c>
       <c r="D48" s="42" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E48" s="42" t="n">
         <v>-2</v>
       </c>
       <c r="F48" s="43" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G48" s="38" t="n"/>
       <c r="H48" s="38" t="n"/>
@@ -2337,13 +2337,13 @@
         </is>
       </c>
       <c r="D49" s="42" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E49" s="42" t="n">
         <v>-1</v>
       </c>
       <c r="F49" s="43" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G49" s="38" t="n"/>
       <c r="H49" s="38" t="n"/>
@@ -2437,13 +2437,13 @@
         </is>
       </c>
       <c r="D52" s="42" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E52" s="42" t="n">
         <v>-1</v>
       </c>
       <c r="F52" s="43" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G52" s="38" t="n"/>
       <c r="H52" s="38" t="n"/>
@@ -2537,13 +2537,13 @@
         </is>
       </c>
       <c r="D55" s="42" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E55" s="42" t="n">
         <v>-2</v>
       </c>
       <c r="F55" s="43" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G55" s="38" t="n"/>
       <c r="H55" s="38" t="n"/>
@@ -2573,13 +2573,13 @@
         </is>
       </c>
       <c r="D56" s="42" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E56" s="42" t="n">
         <v>-1</v>
       </c>
       <c r="F56" s="43" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G56" s="38" t="n"/>
       <c r="H56" s="38" t="n"/>
@@ -2609,13 +2609,13 @@
         </is>
       </c>
       <c r="D57" s="42" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E57" s="42" t="n">
         <v>-2</v>
       </c>
       <c r="F57" s="43" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G57" s="38" t="n"/>
       <c r="H57" s="38" t="n"/>
@@ -2677,13 +2677,13 @@
         </is>
       </c>
       <c r="D59" s="42" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E59" s="42" t="n">
         <v>-1</v>
       </c>
       <c r="F59" s="43" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G59" s="38" t="n"/>
       <c r="H59" s="38" t="n"/>
@@ -2745,13 +2745,13 @@
         </is>
       </c>
       <c r="D61" s="42" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E61" s="42" t="n">
         <v>-1</v>
       </c>
       <c r="F61" s="43" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G61" s="38" t="n"/>
       <c r="H61" s="38" t="n"/>
@@ -2909,13 +2909,13 @@
         </is>
       </c>
       <c r="D66" s="42" t="n">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="E66" s="42" t="n">
         <v>-3</v>
       </c>
       <c r="F66" s="43" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="G66" s="38" t="n"/>
       <c r="H66" s="38" t="n"/>
@@ -2945,13 +2945,13 @@
         </is>
       </c>
       <c r="D67" s="42" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E67" s="42" t="n">
         <v>-1</v>
       </c>
       <c r="F67" s="43" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G67" s="38" t="n"/>
       <c r="H67" s="38" t="n"/>
@@ -3045,13 +3045,13 @@
         </is>
       </c>
       <c r="D70" s="42" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E70" s="42" t="n">
         <v>-1</v>
       </c>
       <c r="F70" s="43" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G70" s="38" t="n"/>
       <c r="H70" s="38" t="n"/>
@@ -4157,13 +4157,13 @@
         </is>
       </c>
       <c r="D105" s="42" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E105" s="42" t="n">
         <v>-12</v>
       </c>
       <c r="F105" s="43" t="n">
-        <v>0</v>
+        <v>-12</v>
       </c>
       <c r="G105" s="38" t="n"/>
       <c r="H105" s="38" t="n"/>
@@ -4225,13 +4225,13 @@
         </is>
       </c>
       <c r="D107" s="42" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="E107" s="42" t="n">
         <v>-12</v>
       </c>
       <c r="F107" s="43" t="n">
-        <v>7</v>
+        <v>-5</v>
       </c>
       <c r="G107" s="38" t="n"/>
       <c r="H107" s="38" t="n"/>
@@ -4261,13 +4261,13 @@
         </is>
       </c>
       <c r="D108" s="42" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E108" s="42" t="n">
         <v>-2</v>
       </c>
       <c r="F108" s="43" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G108" s="38" t="n"/>
       <c r="H108" s="38" t="n"/>
@@ -4519,13 +4519,13 @@
         </is>
       </c>
       <c r="D116" s="42" t="n">
-        <v>-47</v>
+        <v>-83</v>
       </c>
       <c r="E116" s="42" t="n">
         <v>-36</v>
       </c>
       <c r="F116" s="43" t="n">
-        <v>-83</v>
+        <v>-119</v>
       </c>
       <c r="G116" s="38" t="n"/>
       <c r="H116" s="38" t="n"/>
@@ -4555,13 +4555,13 @@
         </is>
       </c>
       <c r="D117" s="42" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E117" s="42" t="n">
         <v>-1</v>
       </c>
       <c r="F117" s="43" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G117" s="38" t="n"/>
       <c r="H117" s="38" t="n"/>
@@ -4655,13 +4655,13 @@
         </is>
       </c>
       <c r="D120" s="42" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E120" s="42" t="n">
         <v>-1</v>
       </c>
       <c r="F120" s="43" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G120" s="38" t="n"/>
       <c r="H120" s="38" t="n"/>
@@ -4819,13 +4819,13 @@
         </is>
       </c>
       <c r="D125" s="42" t="n">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E125" s="42" t="n">
         <v>-1</v>
       </c>
       <c r="F125" s="43" t="n">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G125" s="38" t="n"/>
       <c r="H125" s="38" t="n"/>
@@ -5269,13 +5269,13 @@
         </is>
       </c>
       <c r="D139" s="42" t="n">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E139" s="42" t="n">
         <v>-2</v>
       </c>
       <c r="F139" s="43" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="G139" s="38" t="n"/>
       <c r="H139" s="38" t="n"/>
@@ -5431,13 +5431,13 @@
         </is>
       </c>
       <c r="D144" s="42" t="n">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="E144" s="42" t="n">
         <v>-2</v>
       </c>
       <c r="F144" s="43" t="n">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="G144" s="38" t="n"/>
       <c r="H144" s="38" t="n"/>
@@ -5849,13 +5849,13 @@
         </is>
       </c>
       <c r="D157" s="42" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E157" s="42" t="n">
         <v>-2</v>
       </c>
       <c r="F157" s="43" t="n">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="G157" s="38" t="n"/>
       <c r="H157" s="38" t="n"/>
@@ -6039,13 +6039,13 @@
         </is>
       </c>
       <c r="D163" s="42" t="n">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="E163" s="42" t="n">
         <v>-2</v>
       </c>
       <c r="F163" s="43" t="n">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="G163" s="38" t="n"/>
       <c r="H163" s="38" t="n"/>
@@ -6139,13 +6139,13 @@
         </is>
       </c>
       <c r="D166" s="42" t="n">
-        <v>131</v>
+        <v>119</v>
       </c>
       <c r="E166" s="42" t="n">
         <v>-12</v>
       </c>
       <c r="F166" s="43" t="n">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="G166" s="38" t="n"/>
       <c r="H166" s="38" t="n"/>
@@ -6175,13 +6175,13 @@
         </is>
       </c>
       <c r="D167" s="42" t="n">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="E167" s="42" t="n">
         <v>-3</v>
       </c>
       <c r="F167" s="43" t="n">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="G167" s="38" t="n"/>
       <c r="H167" s="38" t="n"/>
@@ -6399,13 +6399,13 @@
         </is>
       </c>
       <c r="D174" s="42" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E174" s="42" t="n">
         <v>-2</v>
       </c>
       <c r="F174" s="43" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G174" s="38" t="n"/>
       <c r="H174" s="38" t="n"/>
@@ -6467,13 +6467,13 @@
         </is>
       </c>
       <c r="D176" s="42" t="n">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="E176" s="42" t="n">
         <v>-4</v>
       </c>
       <c r="F176" s="43" t="n">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="G176" s="38" t="n"/>
       <c r="H176" s="38" t="n"/>
@@ -6567,13 +6567,13 @@
         </is>
       </c>
       <c r="D179" s="42" t="n">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="E179" s="42" t="n">
         <v>-11</v>
       </c>
       <c r="F179" s="43" t="n">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="G179" s="38" t="n"/>
       <c r="H179" s="38" t="n"/>
@@ -6635,13 +6635,13 @@
         </is>
       </c>
       <c r="D181" s="42" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E181" s="42" t="n">
         <v>-1</v>
       </c>
       <c r="F181" s="43" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G181" s="38" t="n"/>
       <c r="H181" s="38" t="n"/>
@@ -6671,13 +6671,13 @@
         </is>
       </c>
       <c r="D182" s="42" t="n">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E182" s="42" t="n">
         <v>-1</v>
       </c>
       <c r="F182" s="43" t="n">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="G182" s="38" t="n"/>
       <c r="H182" s="38" t="n"/>
@@ -6739,13 +6739,13 @@
         </is>
       </c>
       <c r="D184" s="42" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E184" s="42" t="n">
         <v>-1</v>
       </c>
       <c r="F184" s="43" t="n">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G184" s="38" t="n"/>
       <c r="H184" s="38" t="n"/>
@@ -6839,13 +6839,13 @@
         </is>
       </c>
       <c r="D187" s="42" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="E187" s="42" t="n">
         <v>-15</v>
       </c>
       <c r="F187" s="43" t="n">
-        <v>1</v>
+        <v>-14</v>
       </c>
       <c r="G187" s="38" t="n"/>
       <c r="H187" s="38" t="n"/>
@@ -6939,13 +6939,13 @@
         </is>
       </c>
       <c r="D190" s="42" t="n">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E190" s="42" t="n">
         <v>-1</v>
       </c>
       <c r="F190" s="43" t="n">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="G190" s="38" t="n"/>
       <c r="H190" s="38" t="n"/>
@@ -6975,13 +6975,13 @@
         </is>
       </c>
       <c r="D191" s="42" t="n">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="E191" s="42" t="n">
         <v>-3</v>
       </c>
       <c r="F191" s="43" t="n">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="G191" s="38" t="n"/>
       <c r="H191" s="38" t="n"/>
@@ -7043,13 +7043,13 @@
         </is>
       </c>
       <c r="D193" s="42" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E193" s="42" t="n">
         <v>-1</v>
       </c>
       <c r="F193" s="43" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G193" s="38" t="n"/>
       <c r="H193" s="38" t="n"/>
@@ -7171,13 +7171,13 @@
         </is>
       </c>
       <c r="D197" s="42" t="n">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="E197" s="42" t="n">
         <v>-11</v>
       </c>
       <c r="F197" s="43" t="n">
-        <v>101</v>
+        <v>90</v>
       </c>
       <c r="G197" s="38" t="n"/>
       <c r="H197" s="38" t="n"/>
@@ -7207,13 +7207,13 @@
         </is>
       </c>
       <c r="D198" s="42" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E198" s="42" t="n">
         <v>-1</v>
       </c>
       <c r="F198" s="43" t="n">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G198" s="38" t="n"/>
       <c r="H198" s="38" t="n"/>
@@ -7491,13 +7491,13 @@
         </is>
       </c>
       <c r="D207" s="42" t="n">
-        <v>63</v>
+        <v>43</v>
       </c>
       <c r="E207" s="42" t="n">
         <v>-20</v>
       </c>
       <c r="F207" s="43" t="n">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="G207" s="38" t="n"/>
       <c r="H207" s="38" t="n"/>
@@ -7655,13 +7655,13 @@
         </is>
       </c>
       <c r="D212" s="42" t="n">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E212" s="42" t="n">
         <v>-1</v>
       </c>
       <c r="F212" s="43" t="n">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="G212" s="38" t="n"/>
       <c r="H212" s="38" t="n"/>
@@ -7691,13 +7691,13 @@
         </is>
       </c>
       <c r="D213" s="42" t="n">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E213" s="42" t="n">
         <v>-2</v>
       </c>
       <c r="F213" s="43" t="n">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="G213" s="38" t="n"/>
       <c r="H213" s="38" t="n"/>
@@ -7727,13 +7727,13 @@
         </is>
       </c>
       <c r="D214" s="42" t="n">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="E214" s="42" t="n">
         <v>-1</v>
       </c>
       <c r="F214" s="43" t="n">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="G214" s="38" t="n"/>
       <c r="H214" s="38" t="n"/>
@@ -7763,13 +7763,13 @@
         </is>
       </c>
       <c r="D215" s="42" t="n">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="E215" s="42" t="n">
         <v>-20</v>
       </c>
       <c r="F215" s="43" t="n">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="G215" s="38" t="n"/>
       <c r="H215" s="38" t="n"/>
@@ -7831,13 +7831,13 @@
         </is>
       </c>
       <c r="D217" s="42" t="n">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E217" s="42" t="n">
         <v>-1</v>
       </c>
       <c r="F217" s="43" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G217" s="38" t="n"/>
       <c r="H217" s="38" t="n"/>
@@ -7867,13 +7867,13 @@
         </is>
       </c>
       <c r="D218" s="42" t="n">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="E218" s="42" t="n">
         <v>-3</v>
       </c>
       <c r="F218" s="43" t="n">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="G218" s="38" t="n"/>
       <c r="H218" s="38" t="n"/>
@@ -7935,13 +7935,13 @@
         </is>
       </c>
       <c r="D220" s="42" t="n">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E220" s="42" t="n">
         <v>-2</v>
       </c>
       <c r="F220" s="43" t="n">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="G220" s="38" t="n"/>
       <c r="H220" s="38" t="n"/>
@@ -8099,13 +8099,13 @@
         </is>
       </c>
       <c r="D225" s="42" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E225" s="42" t="n">
         <v>-2</v>
       </c>
       <c r="F225" s="43" t="n">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="G225" s="38" t="n"/>
       <c r="H225" s="38" t="n"/>
@@ -8263,13 +8263,13 @@
         </is>
       </c>
       <c r="D230" s="42" t="n">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E230" s="42" t="n">
         <v>-2</v>
       </c>
       <c r="F230" s="43" t="n">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="G230" s="38" t="n"/>
       <c r="H230" s="38" t="n"/>
@@ -8427,13 +8427,13 @@
         </is>
       </c>
       <c r="D235" s="42" t="n">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E235" s="42" t="n">
         <v>-1</v>
       </c>
       <c r="F235" s="43" t="n">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="G235" s="38" t="n"/>
       <c r="H235" s="38" t="n"/>
@@ -8591,13 +8591,13 @@
         </is>
       </c>
       <c r="D240" s="42" t="n">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="E240" s="42" t="n">
         <v>-8</v>
       </c>
       <c r="F240" s="43" t="n">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="G240" s="38" t="n"/>
       <c r="H240" s="38" t="n"/>
@@ -8659,13 +8659,13 @@
         </is>
       </c>
       <c r="D242" s="42" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E242" s="42" t="n">
         <v>-1</v>
       </c>
       <c r="F242" s="43" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G242" s="38" t="n"/>
       <c r="H242" s="38" t="n"/>
@@ -8759,13 +8759,13 @@
         </is>
       </c>
       <c r="D245" s="42" t="n">
-        <v>854</v>
+        <v>848</v>
       </c>
       <c r="E245" s="42" t="n">
         <v>-6</v>
       </c>
       <c r="F245" s="43" t="n">
-        <v>848</v>
+        <v>842</v>
       </c>
       <c r="G245" s="38" t="n"/>
       <c r="H245" s="38" t="n"/>
@@ -8795,13 +8795,13 @@
         </is>
       </c>
       <c r="D246" s="42" t="n">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="E246" s="42" t="n">
         <v>-2</v>
       </c>
       <c r="F246" s="43" t="n">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="G246" s="38" t="n"/>
       <c r="H246" s="38" t="n"/>
@@ -9051,13 +9051,13 @@
         </is>
       </c>
       <c r="D254" s="42" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E254" s="42" t="n">
         <v>-1</v>
       </c>
       <c r="F254" s="43" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G254" s="38" t="n"/>
       <c r="H254" s="38" t="n"/>
@@ -9245,13 +9245,13 @@
         </is>
       </c>
       <c r="D260" s="42" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E260" s="42" t="n">
         <v>-2</v>
       </c>
       <c r="F260" s="43" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="G260" s="38" t="n"/>
       <c r="H260" s="38" t="n"/>
@@ -9343,13 +9343,13 @@
         </is>
       </c>
       <c r="D263" s="42" t="n">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="E263" s="42" t="n">
         <v>-8</v>
       </c>
       <c r="F263" s="43" t="n">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="G263" s="38" t="n"/>
       <c r="H263" s="38" t="n"/>
@@ -9443,13 +9443,13 @@
         </is>
       </c>
       <c r="D266" s="42" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E266" s="42" t="n">
         <v>-1</v>
       </c>
       <c r="F266" s="43" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G266" s="38" t="n"/>
       <c r="H266" s="38" t="n"/>
@@ -10393,13 +10393,13 @@
         </is>
       </c>
       <c r="D296" s="45" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E296" s="45" t="n">
         <v>-2</v>
       </c>
       <c r="F296" s="43" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G296" s="38" t="n"/>
       <c r="H296" s="38" t="n"/>
@@ -10439,13 +10439,13 @@
         </is>
       </c>
       <c r="D297" s="45" t="n">
-        <v>896</v>
+        <v>894</v>
       </c>
       <c r="E297" s="45" t="n">
         <v>-2</v>
       </c>
       <c r="F297" s="43" t="n">
-        <v>894</v>
+        <v>892</v>
       </c>
       <c r="G297" s="38" t="n"/>
       <c r="H297" s="38" t="n"/>
@@ -10507,13 +10507,13 @@
         </is>
       </c>
       <c r="D299" s="45" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E299" s="45" t="n">
         <v>-2</v>
       </c>
       <c r="F299" s="43" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G299" s="38" t="n"/>
       <c r="H299" s="38" t="n"/>
@@ -10923,13 +10923,13 @@
         </is>
       </c>
       <c r="D311" s="45" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E311" s="45" t="n">
         <v>-2</v>
       </c>
       <c r="F311" s="43" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G311" s="38" t="n"/>
       <c r="H311" s="38" t="n"/>
@@ -10959,13 +10959,13 @@
         </is>
       </c>
       <c r="D312" s="45" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E312" s="45" t="n">
         <v>-2</v>
       </c>
       <c r="F312" s="43" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G312" s="38" t="n"/>
       <c r="H312" s="38" t="n"/>
@@ -11713,13 +11713,13 @@
         </is>
       </c>
       <c r="D337" s="45" t="n">
-        <v>-6</v>
+        <v>-9</v>
       </c>
       <c r="E337" s="45" t="n">
         <v>-3</v>
       </c>
       <c r="F337" s="43" t="n">
-        <v>-9</v>
+        <v>-12</v>
       </c>
       <c r="G337" s="38" t="n"/>
       <c r="H337" s="38" t="n"/>
@@ -11989,13 +11989,13 @@
         </is>
       </c>
       <c r="D346" s="45" t="n">
-        <v>-6</v>
+        <v>-9</v>
       </c>
       <c r="E346" s="45" t="n">
         <v>-3</v>
       </c>
       <c r="F346" s="43" t="n">
-        <v>-9</v>
+        <v>-12</v>
       </c>
       <c r="G346" s="38" t="n"/>
       <c r="H346" s="38" t="n"/>
@@ -12085,13 +12085,13 @@
         </is>
       </c>
       <c r="D349" s="45" t="n">
-        <v>-4</v>
+        <v>-6</v>
       </c>
       <c r="E349" s="45" t="n">
         <v>-2</v>
       </c>
       <c r="F349" s="43" t="n">
-        <v>-6</v>
+        <v>-8</v>
       </c>
       <c r="G349" s="38" t="n"/>
       <c r="H349" s="38" t="n"/>
@@ -12211,13 +12211,13 @@
         </is>
       </c>
       <c r="D353" s="45" t="n">
-        <v>-4</v>
+        <v>-6</v>
       </c>
       <c r="E353" s="45" t="n">
         <v>-2</v>
       </c>
       <c r="F353" s="43" t="n">
-        <v>-6</v>
+        <v>-8</v>
       </c>
       <c r="G353" s="38" t="n"/>
       <c r="H353" s="38" t="n"/>
@@ -12307,13 +12307,13 @@
         </is>
       </c>
       <c r="D356" s="45" t="n">
-        <v>-6</v>
+        <v>-9</v>
       </c>
       <c r="E356" s="45" t="n">
         <v>-3</v>
       </c>
       <c r="F356" s="43" t="n">
-        <v>-9</v>
+        <v>-12</v>
       </c>
       <c r="G356" s="38" t="n"/>
       <c r="H356" s="38" t="n"/>
@@ -12523,13 +12523,13 @@
         </is>
       </c>
       <c r="D363" s="45" t="n">
-        <v>-4</v>
+        <v>-6</v>
       </c>
       <c r="E363" s="45" t="n">
         <v>-2</v>
       </c>
       <c r="F363" s="43" t="n">
-        <v>-6</v>
+        <v>-8</v>
       </c>
       <c r="G363" s="38" t="n"/>
       <c r="H363" s="38" t="n"/>

--- a/Descuentos/Productos_backup.xlsx
+++ b/Descuentos/Productos_backup.xlsx
@@ -1081,13 +1081,13 @@
         </is>
       </c>
       <c r="D11" s="42" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E11" s="42" t="n">
         <v>-1</v>
       </c>
       <c r="F11" s="43" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G11" s="38" t="n"/>
       <c r="H11" s="38" t="n"/>
@@ -1305,13 +1305,13 @@
         </is>
       </c>
       <c r="D18" s="42" t="n">
-        <v>252</v>
+        <v>238</v>
       </c>
       <c r="E18" s="42" t="n">
-        <v>-8</v>
+        <v>-6</v>
       </c>
       <c r="F18" s="43" t="n">
-        <v>244</v>
+        <v>232</v>
       </c>
       <c r="G18" s="38" t="n"/>
       <c r="H18" s="38" t="n"/>
@@ -2337,13 +2337,13 @@
         </is>
       </c>
       <c r="D49" s="42" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E49" s="42" t="n">
         <v>-1</v>
       </c>
       <c r="F49" s="43" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G49" s="38" t="n"/>
       <c r="H49" s="38" t="n"/>
@@ -4157,13 +4157,13 @@
         </is>
       </c>
       <c r="D105" s="42" t="n">
-        <v>0</v>
+        <v>-24</v>
       </c>
       <c r="E105" s="42" t="n">
         <v>-12</v>
       </c>
       <c r="F105" s="43" t="n">
-        <v>-12</v>
+        <v>-36</v>
       </c>
       <c r="G105" s="38" t="n"/>
       <c r="H105" s="38" t="n"/>
@@ -4225,13 +4225,13 @@
         </is>
       </c>
       <c r="D107" s="42" t="n">
-        <v>7</v>
+        <v>-17</v>
       </c>
       <c r="E107" s="42" t="n">
         <v>-12</v>
       </c>
       <c r="F107" s="43" t="n">
-        <v>-5</v>
+        <v>-29</v>
       </c>
       <c r="G107" s="38" t="n"/>
       <c r="H107" s="38" t="n"/>
@@ -4519,13 +4519,13 @@
         </is>
       </c>
       <c r="D116" s="42" t="n">
-        <v>-83</v>
+        <v>-155</v>
       </c>
       <c r="E116" s="42" t="n">
         <v>-36</v>
       </c>
       <c r="F116" s="43" t="n">
-        <v>-119</v>
+        <v>-191</v>
       </c>
       <c r="G116" s="38" t="n"/>
       <c r="H116" s="38" t="n"/>
@@ -6139,13 +6139,13 @@
         </is>
       </c>
       <c r="D166" s="42" t="n">
-        <v>119</v>
+        <v>95</v>
       </c>
       <c r="E166" s="42" t="n">
         <v>-12</v>
       </c>
       <c r="F166" s="43" t="n">
-        <v>107</v>
+        <v>83</v>
       </c>
       <c r="G166" s="38" t="n"/>
       <c r="H166" s="38" t="n"/>
@@ -6567,13 +6567,13 @@
         </is>
       </c>
       <c r="D179" s="42" t="n">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="E179" s="42" t="n">
-        <v>-11</v>
+        <v>-10</v>
       </c>
       <c r="F179" s="43" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="G179" s="38" t="n"/>
       <c r="H179" s="38" t="n"/>
@@ -6839,13 +6839,13 @@
         </is>
       </c>
       <c r="D187" s="42" t="n">
-        <v>1</v>
+        <v>-28</v>
       </c>
       <c r="E187" s="42" t="n">
-        <v>-15</v>
+        <v>-14</v>
       </c>
       <c r="F187" s="43" t="n">
-        <v>-14</v>
+        <v>-42</v>
       </c>
       <c r="G187" s="38" t="n"/>
       <c r="H187" s="38" t="n"/>
@@ -7171,13 +7171,13 @@
         </is>
       </c>
       <c r="D197" s="42" t="n">
-        <v>101</v>
+        <v>80</v>
       </c>
       <c r="E197" s="42" t="n">
-        <v>-11</v>
+        <v>-10</v>
       </c>
       <c r="F197" s="43" t="n">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="G197" s="38" t="n"/>
       <c r="H197" s="38" t="n"/>
@@ -7491,13 +7491,13 @@
         </is>
       </c>
       <c r="D207" s="42" t="n">
-        <v>43</v>
+        <v>3</v>
       </c>
       <c r="E207" s="42" t="n">
         <v>-20</v>
       </c>
       <c r="F207" s="43" t="n">
-        <v>23</v>
+        <v>-17</v>
       </c>
       <c r="G207" s="38" t="n"/>
       <c r="H207" s="38" t="n"/>
@@ -7763,13 +7763,13 @@
         </is>
       </c>
       <c r="D215" s="42" t="n">
-        <v>31</v>
+        <v>-9</v>
       </c>
       <c r="E215" s="42" t="n">
         <v>-20</v>
       </c>
       <c r="F215" s="43" t="n">
-        <v>11</v>
+        <v>-29</v>
       </c>
       <c r="G215" s="38" t="n"/>
       <c r="H215" s="38" t="n"/>
@@ -9343,13 +9343,13 @@
         </is>
       </c>
       <c r="D263" s="42" t="n">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="E263" s="42" t="n">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="F263" s="43" t="n">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="G263" s="38" t="n"/>
       <c r="H263" s="38" t="n"/>
@@ -9443,13 +9443,13 @@
         </is>
       </c>
       <c r="D266" s="42" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E266" s="42" t="n">
         <v>-1</v>
       </c>
       <c r="F266" s="43" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="G266" s="38" t="n"/>
       <c r="H266" s="38" t="n"/>
@@ -10393,13 +10393,13 @@
         </is>
       </c>
       <c r="D296" s="45" t="n">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="E296" s="45" t="n">
         <v>-2</v>
       </c>
       <c r="F296" s="43" t="n">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="G296" s="38" t="n"/>
       <c r="H296" s="38" t="n"/>
@@ -10439,13 +10439,13 @@
         </is>
       </c>
       <c r="D297" s="45" t="n">
-        <v>894</v>
+        <v>890</v>
       </c>
       <c r="E297" s="45" t="n">
         <v>-2</v>
       </c>
       <c r="F297" s="43" t="n">
-        <v>892</v>
+        <v>888</v>
       </c>
       <c r="G297" s="38" t="n"/>
       <c r="H297" s="38" t="n"/>
@@ -10507,13 +10507,13 @@
         </is>
       </c>
       <c r="D299" s="45" t="n">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="E299" s="45" t="n">
         <v>-2</v>
       </c>
       <c r="F299" s="43" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="G299" s="38" t="n"/>
       <c r="H299" s="38" t="n"/>
@@ -10923,13 +10923,13 @@
         </is>
       </c>
       <c r="D311" s="45" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="E311" s="45" t="n">
         <v>-2</v>
       </c>
       <c r="F311" s="43" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="G311" s="38" t="n"/>
       <c r="H311" s="38" t="n"/>
@@ -10959,13 +10959,13 @@
         </is>
       </c>
       <c r="D312" s="45" t="n">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E312" s="45" t="n">
         <v>-2</v>
       </c>
       <c r="F312" s="43" t="n">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="G312" s="38" t="n"/>
       <c r="H312" s="38" t="n"/>
@@ -11713,13 +11713,13 @@
         </is>
       </c>
       <c r="D337" s="45" t="n">
-        <v>-9</v>
+        <v>-15</v>
       </c>
       <c r="E337" s="45" t="n">
         <v>-3</v>
       </c>
       <c r="F337" s="43" t="n">
-        <v>-12</v>
+        <v>-18</v>
       </c>
       <c r="G337" s="38" t="n"/>
       <c r="H337" s="38" t="n"/>
@@ -11989,13 +11989,13 @@
         </is>
       </c>
       <c r="D346" s="45" t="n">
-        <v>-9</v>
+        <v>-15</v>
       </c>
       <c r="E346" s="45" t="n">
         <v>-3</v>
       </c>
       <c r="F346" s="43" t="n">
-        <v>-12</v>
+        <v>-18</v>
       </c>
       <c r="G346" s="38" t="n"/>
       <c r="H346" s="38" t="n"/>
@@ -12085,13 +12085,13 @@
         </is>
       </c>
       <c r="D349" s="45" t="n">
-        <v>-6</v>
+        <v>-10</v>
       </c>
       <c r="E349" s="45" t="n">
         <v>-2</v>
       </c>
       <c r="F349" s="43" t="n">
-        <v>-8</v>
+        <v>-12</v>
       </c>
       <c r="G349" s="38" t="n"/>
       <c r="H349" s="38" t="n"/>
@@ -12211,13 +12211,13 @@
         </is>
       </c>
       <c r="D353" s="45" t="n">
-        <v>-6</v>
+        <v>-10</v>
       </c>
       <c r="E353" s="45" t="n">
         <v>-2</v>
       </c>
       <c r="F353" s="43" t="n">
-        <v>-8</v>
+        <v>-12</v>
       </c>
       <c r="G353" s="38" t="n"/>
       <c r="H353" s="38" t="n"/>
@@ -12307,13 +12307,13 @@
         </is>
       </c>
       <c r="D356" s="45" t="n">
-        <v>-9</v>
+        <v>-15</v>
       </c>
       <c r="E356" s="45" t="n">
         <v>-3</v>
       </c>
       <c r="F356" s="43" t="n">
-        <v>-12</v>
+        <v>-18</v>
       </c>
       <c r="G356" s="38" t="n"/>
       <c r="H356" s="38" t="n"/>
@@ -12523,13 +12523,13 @@
         </is>
       </c>
       <c r="D363" s="45" t="n">
-        <v>-6</v>
+        <v>-10</v>
       </c>
       <c r="E363" s="45" t="n">
         <v>-2</v>
       </c>
       <c r="F363" s="43" t="n">
-        <v>-8</v>
+        <v>-12</v>
       </c>
       <c r="G363" s="38" t="n"/>
       <c r="H363" s="38" t="n"/>

--- a/Descuentos/Productos_backup.xlsx
+++ b/Descuentos/Productos_backup.xlsx
@@ -889,13 +889,13 @@
         </is>
       </c>
       <c r="D5" s="42" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E5" s="42" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="F5" s="43" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="G5" s="38" t="n"/>
       <c r="H5" s="38" t="n"/>
@@ -925,13 +925,13 @@
         </is>
       </c>
       <c r="D6" s="42" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E6" s="42" t="n">
         <v>-1</v>
       </c>
       <c r="F6" s="43" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G6" s="38" t="n"/>
       <c r="H6" s="38" t="n"/>
@@ -1081,13 +1081,13 @@
         </is>
       </c>
       <c r="D11" s="42" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E11" s="42" t="n">
         <v>-1</v>
       </c>
       <c r="F11" s="43" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G11" s="38" t="n"/>
       <c r="H11" s="38" t="n"/>
@@ -1233,13 +1233,13 @@
         </is>
       </c>
       <c r="D16" s="42" t="n">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E16" s="42" t="n">
         <v>-1</v>
       </c>
       <c r="F16" s="43" t="n">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="G16" s="38" t="n"/>
       <c r="H16" s="38" t="n"/>
@@ -1269,13 +1269,13 @@
         </is>
       </c>
       <c r="D17" s="42" t="n">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E17" s="42" t="n">
         <v>-1</v>
       </c>
       <c r="F17" s="43" t="n">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G17" s="38" t="n"/>
       <c r="H17" s="38" t="n"/>
@@ -1305,13 +1305,13 @@
         </is>
       </c>
       <c r="D18" s="42" t="n">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="E18" s="42" t="n">
-        <v>-6</v>
+        <v>-8</v>
       </c>
       <c r="F18" s="43" t="n">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="G18" s="38" t="n"/>
       <c r="H18" s="38" t="n"/>
@@ -1341,13 +1341,13 @@
         </is>
       </c>
       <c r="D19" s="42" t="n">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E19" s="42" t="n">
         <v>-1</v>
       </c>
       <c r="F19" s="43" t="n">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G19" s="38" t="n"/>
       <c r="H19" s="38" t="n"/>
@@ -1441,13 +1441,13 @@
         </is>
       </c>
       <c r="D22" s="42" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E22" s="42" t="n">
-        <v>-1</v>
+        <v>-3</v>
       </c>
       <c r="F22" s="43" t="n">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="G22" s="38" t="n"/>
       <c r="H22" s="38" t="n"/>
@@ -1504,11 +1504,15 @@
           <t xml:space="preserve">Creatine + ELECTROLYTES x 312 grs </t>
         </is>
       </c>
-      <c r="D24" s="41" t="n">
+      <c r="D24" s="42" t="n">
         <v>68</v>
       </c>
-      <c r="E24" s="41" t="n"/>
-      <c r="F24" s="6" t="n"/>
+      <c r="E24" s="42" t="n">
+        <v>-1</v>
+      </c>
+      <c r="F24" s="43" t="n">
+        <v>67</v>
+      </c>
       <c r="G24" s="38" t="n"/>
       <c r="H24" s="38" t="n"/>
       <c r="I24" s="38" t="n"/>
@@ -1589,13 +1593,13 @@
         </is>
       </c>
       <c r="D27" s="42" t="n">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="E27" s="42" t="n">
         <v>-2</v>
       </c>
       <c r="F27" s="43" t="n">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="G27" s="38" t="n"/>
       <c r="H27" s="38" t="n"/>
@@ -1753,13 +1757,13 @@
         </is>
       </c>
       <c r="D32" s="42" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E32" s="42" t="n">
         <v>-2</v>
       </c>
       <c r="F32" s="43" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G32" s="38" t="n"/>
       <c r="H32" s="38" t="n"/>
@@ -1789,13 +1793,13 @@
         </is>
       </c>
       <c r="D33" s="42" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="E33" s="42" t="n">
         <v>-3</v>
       </c>
       <c r="F33" s="43" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="G33" s="38" t="n"/>
       <c r="H33" s="38" t="n"/>
@@ -1825,13 +1829,13 @@
         </is>
       </c>
       <c r="D34" s="42" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E34" s="42" t="n">
         <v>-1</v>
       </c>
       <c r="F34" s="43" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G34" s="38" t="n"/>
       <c r="H34" s="38" t="n"/>
@@ -1893,13 +1897,13 @@
         </is>
       </c>
       <c r="D36" s="42" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E36" s="42" t="n">
         <v>-1</v>
       </c>
       <c r="F36" s="43" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G36" s="38" t="n"/>
       <c r="H36" s="38" t="n"/>
@@ -1929,13 +1933,13 @@
         </is>
       </c>
       <c r="D37" s="42" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E37" s="42" t="n">
         <v>-1</v>
       </c>
       <c r="F37" s="43" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G37" s="38" t="n"/>
       <c r="H37" s="38" t="n"/>
@@ -2061,13 +2065,13 @@
         </is>
       </c>
       <c r="D41" s="42" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E41" s="42" t="n">
         <v>-1</v>
       </c>
       <c r="F41" s="43" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G41" s="38" t="n"/>
       <c r="H41" s="38" t="n"/>
@@ -2097,13 +2101,13 @@
         </is>
       </c>
       <c r="D42" s="42" t="n">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="E42" s="42" t="n">
         <v>-1</v>
       </c>
       <c r="F42" s="43" t="n">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="G42" s="38" t="n"/>
       <c r="H42" s="38" t="n"/>
@@ -2161,13 +2165,13 @@
         </is>
       </c>
       <c r="D44" s="42" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E44" s="42" t="n">
-        <v>-1</v>
+        <v>-3</v>
       </c>
       <c r="F44" s="43" t="n">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="G44" s="38" t="n"/>
       <c r="H44" s="38" t="n"/>
@@ -2197,13 +2201,13 @@
         </is>
       </c>
       <c r="D45" s="42" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E45" s="42" t="n">
         <v>-1</v>
       </c>
       <c r="F45" s="43" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G45" s="38" t="n"/>
       <c r="H45" s="38" t="n"/>
@@ -2233,13 +2237,13 @@
         </is>
       </c>
       <c r="D46" s="42" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E46" s="42" t="n">
         <v>-1</v>
       </c>
       <c r="F46" s="43" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G46" s="38" t="n"/>
       <c r="H46" s="38" t="n"/>
@@ -2301,13 +2305,13 @@
         </is>
       </c>
       <c r="D48" s="42" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E48" s="42" t="n">
         <v>-2</v>
       </c>
       <c r="F48" s="43" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G48" s="38" t="n"/>
       <c r="H48" s="38" t="n"/>
@@ -2337,13 +2341,13 @@
         </is>
       </c>
       <c r="D49" s="42" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E49" s="42" t="n">
         <v>-1</v>
       </c>
       <c r="F49" s="43" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G49" s="38" t="n"/>
       <c r="H49" s="38" t="n"/>
@@ -2437,13 +2441,13 @@
         </is>
       </c>
       <c r="D52" s="42" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E52" s="42" t="n">
         <v>-1</v>
       </c>
       <c r="F52" s="43" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G52" s="38" t="n"/>
       <c r="H52" s="38" t="n"/>
@@ -2537,13 +2541,13 @@
         </is>
       </c>
       <c r="D55" s="42" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E55" s="42" t="n">
         <v>-2</v>
       </c>
       <c r="F55" s="43" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G55" s="38" t="n"/>
       <c r="H55" s="38" t="n"/>
@@ -2573,13 +2577,13 @@
         </is>
       </c>
       <c r="D56" s="42" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E56" s="42" t="n">
         <v>-1</v>
       </c>
       <c r="F56" s="43" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G56" s="38" t="n"/>
       <c r="H56" s="38" t="n"/>
@@ -2609,13 +2613,13 @@
         </is>
       </c>
       <c r="D57" s="42" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E57" s="42" t="n">
         <v>-2</v>
       </c>
       <c r="F57" s="43" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G57" s="38" t="n"/>
       <c r="H57" s="38" t="n"/>
@@ -2677,13 +2681,13 @@
         </is>
       </c>
       <c r="D59" s="42" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E59" s="42" t="n">
         <v>-1</v>
       </c>
       <c r="F59" s="43" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G59" s="38" t="n"/>
       <c r="H59" s="38" t="n"/>
@@ -2745,13 +2749,13 @@
         </is>
       </c>
       <c r="D61" s="42" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E61" s="42" t="n">
         <v>-1</v>
       </c>
       <c r="F61" s="43" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G61" s="38" t="n"/>
       <c r="H61" s="38" t="n"/>
@@ -2909,13 +2913,13 @@
         </is>
       </c>
       <c r="D66" s="42" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="E66" s="42" t="n">
         <v>-3</v>
       </c>
       <c r="F66" s="43" t="n">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="G66" s="38" t="n"/>
       <c r="H66" s="38" t="n"/>
@@ -2945,13 +2949,13 @@
         </is>
       </c>
       <c r="D67" s="42" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E67" s="42" t="n">
         <v>-1</v>
       </c>
       <c r="F67" s="43" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G67" s="38" t="n"/>
       <c r="H67" s="38" t="n"/>
@@ -3015,8 +3019,12 @@
       <c r="D69" s="42" t="n">
         <v>34</v>
       </c>
-      <c r="E69" s="42" t="n"/>
-      <c r="F69" s="43" t="n"/>
+      <c r="E69" s="42" t="n">
+        <v>-1</v>
+      </c>
+      <c r="F69" s="43" t="n">
+        <v>33</v>
+      </c>
       <c r="G69" s="38" t="n"/>
       <c r="H69" s="38" t="n"/>
       <c r="I69" s="38" t="n"/>
@@ -3045,13 +3053,13 @@
         </is>
       </c>
       <c r="D70" s="42" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E70" s="42" t="n">
         <v>-1</v>
       </c>
       <c r="F70" s="43" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G70" s="38" t="n"/>
       <c r="H70" s="38" t="n"/>
@@ -4157,13 +4165,13 @@
         </is>
       </c>
       <c r="D105" s="42" t="n">
-        <v>-24</v>
+        <v>-36</v>
       </c>
       <c r="E105" s="42" t="n">
         <v>-12</v>
       </c>
       <c r="F105" s="43" t="n">
-        <v>-36</v>
+        <v>-48</v>
       </c>
       <c r="G105" s="38" t="n"/>
       <c r="H105" s="38" t="n"/>
@@ -4225,13 +4233,13 @@
         </is>
       </c>
       <c r="D107" s="42" t="n">
-        <v>-17</v>
+        <v>-29</v>
       </c>
       <c r="E107" s="42" t="n">
         <v>-12</v>
       </c>
       <c r="F107" s="43" t="n">
-        <v>-29</v>
+        <v>-41</v>
       </c>
       <c r="G107" s="38" t="n"/>
       <c r="H107" s="38" t="n"/>
@@ -4261,13 +4269,13 @@
         </is>
       </c>
       <c r="D108" s="42" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E108" s="42" t="n">
         <v>-2</v>
       </c>
       <c r="F108" s="43" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G108" s="38" t="n"/>
       <c r="H108" s="38" t="n"/>
@@ -4519,13 +4527,13 @@
         </is>
       </c>
       <c r="D116" s="42" t="n">
-        <v>-155</v>
+        <v>-191</v>
       </c>
       <c r="E116" s="42" t="n">
         <v>-36</v>
       </c>
       <c r="F116" s="43" t="n">
-        <v>-191</v>
+        <v>-227</v>
       </c>
       <c r="G116" s="38" t="n"/>
       <c r="H116" s="38" t="n"/>
@@ -4555,13 +4563,13 @@
         </is>
       </c>
       <c r="D117" s="42" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E117" s="42" t="n">
         <v>-1</v>
       </c>
       <c r="F117" s="43" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G117" s="38" t="n"/>
       <c r="H117" s="38" t="n"/>
@@ -4655,13 +4663,13 @@
         </is>
       </c>
       <c r="D120" s="42" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E120" s="42" t="n">
         <v>-1</v>
       </c>
       <c r="F120" s="43" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G120" s="38" t="n"/>
       <c r="H120" s="38" t="n"/>
@@ -4819,13 +4827,13 @@
         </is>
       </c>
       <c r="D125" s="42" t="n">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E125" s="42" t="n">
         <v>-1</v>
       </c>
       <c r="F125" s="43" t="n">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G125" s="38" t="n"/>
       <c r="H125" s="38" t="n"/>
@@ -5269,13 +5277,13 @@
         </is>
       </c>
       <c r="D139" s="42" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E139" s="42" t="n">
         <v>-2</v>
       </c>
       <c r="F139" s="43" t="n">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="G139" s="38" t="n"/>
       <c r="H139" s="38" t="n"/>
@@ -5431,13 +5439,13 @@
         </is>
       </c>
       <c r="D144" s="42" t="n">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E144" s="42" t="n">
         <v>-2</v>
       </c>
       <c r="F144" s="43" t="n">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="G144" s="38" t="n"/>
       <c r="H144" s="38" t="n"/>
@@ -5849,13 +5857,13 @@
         </is>
       </c>
       <c r="D157" s="42" t="n">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E157" s="42" t="n">
         <v>-2</v>
       </c>
       <c r="F157" s="43" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="G157" s="38" t="n"/>
       <c r="H157" s="38" t="n"/>
@@ -6039,13 +6047,13 @@
         </is>
       </c>
       <c r="D163" s="42" t="n">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="E163" s="42" t="n">
         <v>-2</v>
       </c>
       <c r="F163" s="43" t="n">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="G163" s="38" t="n"/>
       <c r="H163" s="38" t="n"/>
@@ -6139,13 +6147,13 @@
         </is>
       </c>
       <c r="D166" s="42" t="n">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="E166" s="42" t="n">
         <v>-12</v>
       </c>
       <c r="F166" s="43" t="n">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="G166" s="38" t="n"/>
       <c r="H166" s="38" t="n"/>
@@ -6175,13 +6183,13 @@
         </is>
       </c>
       <c r="D167" s="42" t="n">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="E167" s="42" t="n">
         <v>-3</v>
       </c>
       <c r="F167" s="43" t="n">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="G167" s="38" t="n"/>
       <c r="H167" s="38" t="n"/>
@@ -6399,13 +6407,13 @@
         </is>
       </c>
       <c r="D174" s="42" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E174" s="42" t="n">
         <v>-2</v>
       </c>
       <c r="F174" s="43" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G174" s="38" t="n"/>
       <c r="H174" s="38" t="n"/>
@@ -6467,13 +6475,13 @@
         </is>
       </c>
       <c r="D176" s="42" t="n">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E176" s="42" t="n">
         <v>-4</v>
       </c>
       <c r="F176" s="43" t="n">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="G176" s="38" t="n"/>
       <c r="H176" s="38" t="n"/>
@@ -6567,13 +6575,13 @@
         </is>
       </c>
       <c r="D179" s="42" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E179" s="42" t="n">
-        <v>-10</v>
+        <v>-11</v>
       </c>
       <c r="F179" s="43" t="n">
-        <v>0</v>
+        <v>-11</v>
       </c>
       <c r="G179" s="38" t="n"/>
       <c r="H179" s="38" t="n"/>
@@ -6635,13 +6643,13 @@
         </is>
       </c>
       <c r="D181" s="42" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E181" s="42" t="n">
         <v>-1</v>
       </c>
       <c r="F181" s="43" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G181" s="38" t="n"/>
       <c r="H181" s="38" t="n"/>
@@ -6671,13 +6679,13 @@
         </is>
       </c>
       <c r="D182" s="42" t="n">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E182" s="42" t="n">
         <v>-1</v>
       </c>
       <c r="F182" s="43" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G182" s="38" t="n"/>
       <c r="H182" s="38" t="n"/>
@@ -6739,13 +6747,13 @@
         </is>
       </c>
       <c r="D184" s="42" t="n">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E184" s="42" t="n">
         <v>-1</v>
       </c>
       <c r="F184" s="43" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G184" s="38" t="n"/>
       <c r="H184" s="38" t="n"/>
@@ -6839,13 +6847,13 @@
         </is>
       </c>
       <c r="D187" s="42" t="n">
-        <v>-28</v>
+        <v>-42</v>
       </c>
       <c r="E187" s="42" t="n">
-        <v>-14</v>
+        <v>-15</v>
       </c>
       <c r="F187" s="43" t="n">
-        <v>-42</v>
+        <v>-57</v>
       </c>
       <c r="G187" s="38" t="n"/>
       <c r="H187" s="38" t="n"/>
@@ -6939,13 +6947,13 @@
         </is>
       </c>
       <c r="D190" s="42" t="n">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E190" s="42" t="n">
         <v>-1</v>
       </c>
       <c r="F190" s="43" t="n">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="G190" s="38" t="n"/>
       <c r="H190" s="38" t="n"/>
@@ -6975,13 +6983,13 @@
         </is>
       </c>
       <c r="D191" s="42" t="n">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="E191" s="42" t="n">
         <v>-3</v>
       </c>
       <c r="F191" s="43" t="n">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="G191" s="38" t="n"/>
       <c r="H191" s="38" t="n"/>
@@ -7043,13 +7051,13 @@
         </is>
       </c>
       <c r="D193" s="42" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E193" s="42" t="n">
         <v>-1</v>
       </c>
       <c r="F193" s="43" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G193" s="38" t="n"/>
       <c r="H193" s="38" t="n"/>
@@ -7171,13 +7179,13 @@
         </is>
       </c>
       <c r="D197" s="42" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="E197" s="42" t="n">
-        <v>-10</v>
+        <v>-11</v>
       </c>
       <c r="F197" s="43" t="n">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="G197" s="38" t="n"/>
       <c r="H197" s="38" t="n"/>
@@ -7207,13 +7215,13 @@
         </is>
       </c>
       <c r="D198" s="42" t="n">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E198" s="42" t="n">
         <v>-1</v>
       </c>
       <c r="F198" s="43" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G198" s="38" t="n"/>
       <c r="H198" s="38" t="n"/>
@@ -7491,13 +7499,13 @@
         </is>
       </c>
       <c r="D207" s="42" t="n">
-        <v>3</v>
+        <v>-17</v>
       </c>
       <c r="E207" s="42" t="n">
         <v>-20</v>
       </c>
       <c r="F207" s="43" t="n">
-        <v>-17</v>
+        <v>-37</v>
       </c>
       <c r="G207" s="38" t="n"/>
       <c r="H207" s="38" t="n"/>
@@ -7655,13 +7663,13 @@
         </is>
       </c>
       <c r="D212" s="42" t="n">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E212" s="42" t="n">
         <v>-1</v>
       </c>
       <c r="F212" s="43" t="n">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="G212" s="38" t="n"/>
       <c r="H212" s="38" t="n"/>
@@ -7691,13 +7699,13 @@
         </is>
       </c>
       <c r="D213" s="42" t="n">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E213" s="42" t="n">
         <v>-2</v>
       </c>
       <c r="F213" s="43" t="n">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="G213" s="38" t="n"/>
       <c r="H213" s="38" t="n"/>
@@ -7727,13 +7735,13 @@
         </is>
       </c>
       <c r="D214" s="42" t="n">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="E214" s="42" t="n">
         <v>-1</v>
       </c>
       <c r="F214" s="43" t="n">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="G214" s="38" t="n"/>
       <c r="H214" s="38" t="n"/>
@@ -7763,13 +7771,13 @@
         </is>
       </c>
       <c r="D215" s="42" t="n">
-        <v>-9</v>
+        <v>-29</v>
       </c>
       <c r="E215" s="42" t="n">
         <v>-20</v>
       </c>
       <c r="F215" s="43" t="n">
-        <v>-29</v>
+        <v>-49</v>
       </c>
       <c r="G215" s="38" t="n"/>
       <c r="H215" s="38" t="n"/>
@@ -7831,13 +7839,13 @@
         </is>
       </c>
       <c r="D217" s="42" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E217" s="42" t="n">
         <v>-1</v>
       </c>
       <c r="F217" s="43" t="n">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="G217" s="38" t="n"/>
       <c r="H217" s="38" t="n"/>
@@ -7867,13 +7875,13 @@
         </is>
       </c>
       <c r="D218" s="42" t="n">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="E218" s="42" t="n">
         <v>-3</v>
       </c>
       <c r="F218" s="43" t="n">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="G218" s="38" t="n"/>
       <c r="H218" s="38" t="n"/>
@@ -7935,13 +7943,13 @@
         </is>
       </c>
       <c r="D220" s="42" t="n">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="E220" s="42" t="n">
         <v>-2</v>
       </c>
       <c r="F220" s="43" t="n">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="G220" s="38" t="n"/>
       <c r="H220" s="38" t="n"/>
@@ -8099,13 +8107,13 @@
         </is>
       </c>
       <c r="D225" s="42" t="n">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E225" s="42" t="n">
         <v>-2</v>
       </c>
       <c r="F225" s="43" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="G225" s="38" t="n"/>
       <c r="H225" s="38" t="n"/>
@@ -8263,13 +8271,13 @@
         </is>
       </c>
       <c r="D230" s="42" t="n">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="E230" s="42" t="n">
         <v>-2</v>
       </c>
       <c r="F230" s="43" t="n">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="G230" s="38" t="n"/>
       <c r="H230" s="38" t="n"/>
@@ -8427,13 +8435,13 @@
         </is>
       </c>
       <c r="D235" s="42" t="n">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E235" s="42" t="n">
         <v>-1</v>
       </c>
       <c r="F235" s="43" t="n">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G235" s="38" t="n"/>
       <c r="H235" s="38" t="n"/>
@@ -8591,13 +8599,13 @@
         </is>
       </c>
       <c r="D240" s="42" t="n">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="E240" s="42" t="n">
         <v>-8</v>
       </c>
       <c r="F240" s="43" t="n">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="G240" s="38" t="n"/>
       <c r="H240" s="38" t="n"/>
@@ -8659,13 +8667,13 @@
         </is>
       </c>
       <c r="D242" s="42" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E242" s="42" t="n">
         <v>-1</v>
       </c>
       <c r="F242" s="43" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G242" s="38" t="n"/>
       <c r="H242" s="38" t="n"/>
@@ -8759,13 +8767,13 @@
         </is>
       </c>
       <c r="D245" s="42" t="n">
-        <v>848</v>
+        <v>842</v>
       </c>
       <c r="E245" s="42" t="n">
         <v>-6</v>
       </c>
       <c r="F245" s="43" t="n">
-        <v>842</v>
+        <v>836</v>
       </c>
       <c r="G245" s="38" t="n"/>
       <c r="H245" s="38" t="n"/>
@@ -8795,13 +8803,13 @@
         </is>
       </c>
       <c r="D246" s="42" t="n">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="E246" s="42" t="n">
         <v>-2</v>
       </c>
       <c r="F246" s="43" t="n">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="G246" s="38" t="n"/>
       <c r="H246" s="38" t="n"/>
@@ -9051,13 +9059,13 @@
         </is>
       </c>
       <c r="D254" s="42" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E254" s="42" t="n">
         <v>-1</v>
       </c>
       <c r="F254" s="43" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G254" s="38" t="n"/>
       <c r="H254" s="38" t="n"/>
@@ -9245,13 +9253,13 @@
         </is>
       </c>
       <c r="D260" s="42" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E260" s="42" t="n">
         <v>-2</v>
       </c>
       <c r="F260" s="43" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="G260" s="38" t="n"/>
       <c r="H260" s="38" t="n"/>
@@ -9343,13 +9351,13 @@
         </is>
       </c>
       <c r="D263" s="42" t="n">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="E263" s="42" t="n">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="F263" s="43" t="n">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="G263" s="38" t="n"/>
       <c r="H263" s="38" t="n"/>
@@ -9443,13 +9451,13 @@
         </is>
       </c>
       <c r="D266" s="42" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E266" s="42" t="n">
         <v>-1</v>
       </c>
       <c r="F266" s="43" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G266" s="38" t="n"/>
       <c r="H266" s="38" t="n"/>
@@ -10393,13 +10401,13 @@
         </is>
       </c>
       <c r="D296" s="45" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E296" s="45" t="n">
         <v>-2</v>
       </c>
       <c r="F296" s="43" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="G296" s="38" t="n"/>
       <c r="H296" s="38" t="n"/>
@@ -10439,13 +10447,13 @@
         </is>
       </c>
       <c r="D297" s="45" t="n">
-        <v>890</v>
+        <v>888</v>
       </c>
       <c r="E297" s="45" t="n">
         <v>-2</v>
       </c>
       <c r="F297" s="43" t="n">
-        <v>888</v>
+        <v>886</v>
       </c>
       <c r="G297" s="38" t="n"/>
       <c r="H297" s="38" t="n"/>
@@ -10507,13 +10515,13 @@
         </is>
       </c>
       <c r="D299" s="45" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E299" s="45" t="n">
         <v>-2</v>
       </c>
       <c r="F299" s="43" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="G299" s="38" t="n"/>
       <c r="H299" s="38" t="n"/>
@@ -10923,13 +10931,13 @@
         </is>
       </c>
       <c r="D311" s="45" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E311" s="45" t="n">
         <v>-2</v>
       </c>
       <c r="F311" s="43" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G311" s="38" t="n"/>
       <c r="H311" s="38" t="n"/>
@@ -10959,13 +10967,13 @@
         </is>
       </c>
       <c r="D312" s="45" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E312" s="45" t="n">
         <v>-2</v>
       </c>
       <c r="F312" s="43" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G312" s="38" t="n"/>
       <c r="H312" s="38" t="n"/>
@@ -11713,13 +11721,13 @@
         </is>
       </c>
       <c r="D337" s="45" t="n">
-        <v>-15</v>
+        <v>-18</v>
       </c>
       <c r="E337" s="45" t="n">
         <v>-3</v>
       </c>
       <c r="F337" s="43" t="n">
-        <v>-18</v>
+        <v>-21</v>
       </c>
       <c r="G337" s="38" t="n"/>
       <c r="H337" s="38" t="n"/>
@@ -11989,13 +11997,13 @@
         </is>
       </c>
       <c r="D346" s="45" t="n">
-        <v>-15</v>
+        <v>-18</v>
       </c>
       <c r="E346" s="45" t="n">
         <v>-3</v>
       </c>
       <c r="F346" s="43" t="n">
-        <v>-18</v>
+        <v>-21</v>
       </c>
       <c r="G346" s="38" t="n"/>
       <c r="H346" s="38" t="n"/>
@@ -12085,13 +12093,13 @@
         </is>
       </c>
       <c r="D349" s="45" t="n">
-        <v>-10</v>
+        <v>-12</v>
       </c>
       <c r="E349" s="45" t="n">
         <v>-2</v>
       </c>
       <c r="F349" s="43" t="n">
-        <v>-12</v>
+        <v>-14</v>
       </c>
       <c r="G349" s="38" t="n"/>
       <c r="H349" s="38" t="n"/>
@@ -12211,13 +12219,13 @@
         </is>
       </c>
       <c r="D353" s="45" t="n">
-        <v>-10</v>
+        <v>-12</v>
       </c>
       <c r="E353" s="45" t="n">
         <v>-2</v>
       </c>
       <c r="F353" s="43" t="n">
-        <v>-12</v>
+        <v>-14</v>
       </c>
       <c r="G353" s="38" t="n"/>
       <c r="H353" s="38" t="n"/>
@@ -12307,13 +12315,13 @@
         </is>
       </c>
       <c r="D356" s="45" t="n">
-        <v>-15</v>
+        <v>-18</v>
       </c>
       <c r="E356" s="45" t="n">
         <v>-3</v>
       </c>
       <c r="F356" s="43" t="n">
-        <v>-18</v>
+        <v>-21</v>
       </c>
       <c r="G356" s="38" t="n"/>
       <c r="H356" s="38" t="n"/>
@@ -12523,13 +12531,13 @@
         </is>
       </c>
       <c r="D363" s="45" t="n">
-        <v>-10</v>
+        <v>-12</v>
       </c>
       <c r="E363" s="45" t="n">
         <v>-2</v>
       </c>
       <c r="F363" s="43" t="n">
-        <v>-12</v>
+        <v>-14</v>
       </c>
       <c r="G363" s="38" t="n"/>
       <c r="H363" s="38" t="n"/>

--- a/Descuentos/Productos_backup.xlsx
+++ b/Descuentos/Productos_backup.xlsx
@@ -111,7 +111,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="15">
+  <borders count="17">
     <border>
       <left/>
       <right/>
@@ -279,11 +279,35 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFc6c6c6"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFc6c6c6"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFc6c6c6"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
@@ -420,6 +444,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -824,8 +849,8 @@
         </is>
       </c>
       <c r="D1" s="44" t="n"/>
-      <c r="E1" s="45" t="n"/>
-      <c r="F1" s="1" t="n"/>
+      <c r="E1" s="44" t="n"/>
+      <c r="F1" s="44" t="n"/>
       <c r="G1" s="1" t="n"/>
       <c r="H1" s="1" t="n"/>
       <c r="I1" s="1" t="n"/>
@@ -841,10 +866,7 @@
     <row r="2" ht="18.75" customHeight="1">
       <c r="A2" s="46" t="n"/>
       <c r="B2" s="46" t="n"/>
-      <c r="C2" s="47" t="n"/>
-      <c r="D2" s="48" t="n"/>
-      <c r="E2" s="49" t="n"/>
-      <c r="F2" s="1" t="n"/>
+      <c r="C2" s="50" t="n"/>
       <c r="G2" s="1" t="n"/>
       <c r="H2" s="1" t="n"/>
       <c r="I2" s="1" t="n"/>
@@ -1226,9 +1248,13 @@
           <t>Creatine 150 g UT</t>
         </is>
       </c>
-      <c r="C17" s="20" t="n"/>
+      <c r="C17" s="20" t="n">
+        <v>25</v>
+      </c>
       <c r="D17" s="20" t="n"/>
-      <c r="E17" s="19" t="n"/>
+      <c r="E17" s="19" t="n">
+        <v>25</v>
+      </c>
       <c r="F17" s="1" t="n"/>
       <c r="G17" s="1" t="n"/>
       <c r="H17" s="1" t="n"/>

--- a/Descuentos/Productos_backup.xlsx
+++ b/Descuentos/Productos_backup.xlsx
@@ -1023,9 +1023,13 @@
           <t>Beta Alanine</t>
         </is>
       </c>
-      <c r="C8" s="18" t="n"/>
+      <c r="C8" s="18" t="n">
+        <v>-2</v>
+      </c>
       <c r="D8" s="18" t="n"/>
-      <c r="E8" s="19" t="n"/>
+      <c r="E8" s="19" t="n">
+        <v>-2</v>
+      </c>
       <c r="F8" s="1" t="n"/>
       <c r="G8" s="1" t="n"/>
       <c r="H8" s="1" t="n"/>
@@ -1148,9 +1152,13 @@
           <t>CITRATO MAGNESIO  * 60 UT</t>
         </is>
       </c>
-      <c r="C13" s="18" t="n"/>
+      <c r="C13" s="18" t="n">
+        <v>-17</v>
+      </c>
       <c r="D13" s="18" t="n"/>
-      <c r="E13" s="19" t="n"/>
+      <c r="E13" s="19" t="n">
+        <v>-17</v>
+      </c>
       <c r="F13" s="1" t="n"/>
       <c r="G13" s="1" t="n"/>
       <c r="H13" s="1" t="n"/>
@@ -1223,9 +1231,13 @@
           <t>CREATINA EN COMPRIMIDOS ULTRA TECH</t>
         </is>
       </c>
-      <c r="C16" s="20" t="n"/>
+      <c r="C16" s="20" t="n">
+        <v>-30</v>
+      </c>
       <c r="D16" s="20" t="n"/>
-      <c r="E16" s="19" t="n"/>
+      <c r="E16" s="19" t="n">
+        <v>-30</v>
+      </c>
       <c r="F16" s="1" t="n"/>
       <c r="G16" s="1" t="n"/>
       <c r="H16" s="1" t="n"/>
@@ -1249,11 +1261,11 @@
         </is>
       </c>
       <c r="C17" s="20" t="n">
-        <v>25</v>
+        <v>-21</v>
       </c>
       <c r="D17" s="20" t="n"/>
       <c r="E17" s="19" t="n">
-        <v>25</v>
+        <v>-21</v>
       </c>
       <c r="F17" s="1" t="n"/>
       <c r="G17" s="1" t="n"/>
@@ -1277,9 +1289,13 @@
           <t>Creatine 300 g UT</t>
         </is>
       </c>
-      <c r="C18" s="20" t="n"/>
+      <c r="C18" s="20" t="n">
+        <v>-79</v>
+      </c>
       <c r="D18" s="20" t="n"/>
-      <c r="E18" s="19" t="n"/>
+      <c r="E18" s="19" t="n">
+        <v>-79</v>
+      </c>
       <c r="F18" s="1" t="n"/>
       <c r="G18" s="1" t="n"/>
       <c r="H18" s="1" t="n"/>
@@ -1302,9 +1318,13 @@
           <t>Creatine 500 g UT</t>
         </is>
       </c>
-      <c r="C19" s="20" t="n"/>
+      <c r="C19" s="20" t="n">
+        <v>-23</v>
+      </c>
       <c r="D19" s="20" t="n"/>
-      <c r="E19" s="19" t="n"/>
+      <c r="E19" s="19" t="n">
+        <v>-23</v>
+      </c>
       <c r="F19" s="1" t="n"/>
       <c r="G19" s="1" t="n"/>
       <c r="H19" s="1" t="n"/>
@@ -1377,9 +1397,13 @@
           <t>SABORIZADA CREATINA 300 G ULTRA TECH FRUTOS ROJOS C/ LIMON</t>
         </is>
       </c>
-      <c r="C22" s="20" t="n"/>
+      <c r="C22" s="20" t="n">
+        <v>-28</v>
+      </c>
       <c r="D22" s="20" t="n"/>
-      <c r="E22" s="19" t="n"/>
+      <c r="E22" s="19" t="n">
+        <v>-28</v>
+      </c>
       <c r="F22" s="1" t="n"/>
       <c r="G22" s="1" t="n"/>
       <c r="H22" s="1" t="n"/>
@@ -1652,9 +1676,13 @@
           <t>FAT BURNER FOR MEN X 60 CAPS ULTRA TECH</t>
         </is>
       </c>
-      <c r="C33" s="20" t="n"/>
+      <c r="C33" s="20" t="n">
+        <v>-7</v>
+      </c>
       <c r="D33" s="20" t="n"/>
-      <c r="E33" s="19" t="n"/>
+      <c r="E33" s="19" t="n">
+        <v>-7</v>
+      </c>
       <c r="F33" s="1" t="n"/>
       <c r="G33" s="1" t="n"/>
       <c r="H33" s="1" t="n"/>
@@ -1677,9 +1705,13 @@
           <t>FAT BURNER WOMEN X 60 CAPS ULTRA TECH</t>
         </is>
       </c>
-      <c r="C34" s="20" t="n"/>
+      <c r="C34" s="20" t="n">
+        <v>-52</v>
+      </c>
       <c r="D34" s="20" t="n"/>
-      <c r="E34" s="19" t="n"/>
+      <c r="E34" s="19" t="n">
+        <v>-52</v>
+      </c>
       <c r="F34" s="1" t="n"/>
       <c r="G34" s="1" t="n"/>
       <c r="H34" s="1" t="n"/>
@@ -1827,9 +1859,13 @@
           <t xml:space="preserve">Lipo stack UT </t>
         </is>
       </c>
-      <c r="C40" s="18" t="n"/>
+      <c r="C40" s="18" t="n">
+        <v>-2</v>
+      </c>
       <c r="D40" s="18" t="n"/>
-      <c r="E40" s="19" t="n"/>
+      <c r="E40" s="19" t="n">
+        <v>-2</v>
+      </c>
       <c r="F40" s="1" t="n"/>
       <c r="G40" s="1" t="n"/>
       <c r="H40" s="1" t="n"/>
@@ -1902,9 +1938,13 @@
           <t>MAGNESIO TRIPLE * 180GR LIMON UT</t>
         </is>
       </c>
-      <c r="C43" s="18" t="n"/>
+      <c r="C43" s="18" t="n">
+        <v>-21</v>
+      </c>
       <c r="D43" s="18" t="n"/>
-      <c r="E43" s="19" t="n"/>
+      <c r="E43" s="19" t="n">
+        <v>-21</v>
+      </c>
       <c r="F43" s="1" t="n"/>
       <c r="G43" s="1" t="n"/>
       <c r="H43" s="1" t="n"/>
@@ -1927,9 +1967,13 @@
           <t>MULTI COLLAGEN X 405 GR ULTRA TECH</t>
         </is>
       </c>
-      <c r="C44" s="20" t="n"/>
+      <c r="C44" s="20" t="n">
+        <v>-7</v>
+      </c>
       <c r="D44" s="20" t="n"/>
-      <c r="E44" s="19" t="n"/>
+      <c r="E44" s="19" t="n">
+        <v>-7</v>
+      </c>
       <c r="F44" s="1" t="n"/>
       <c r="G44" s="1" t="n"/>
       <c r="H44" s="1" t="n"/>
@@ -1952,9 +1996,13 @@
           <t>Multivitaminas y minerales con ginseng UT</t>
         </is>
       </c>
-      <c r="C45" s="20" t="n"/>
+      <c r="C45" s="20" t="n">
+        <v>-7</v>
+      </c>
       <c r="D45" s="20" t="n"/>
-      <c r="E45" s="19" t="n"/>
+      <c r="E45" s="19" t="n">
+        <v>-7</v>
+      </c>
       <c r="F45" s="1" t="n"/>
       <c r="G45" s="1" t="n"/>
       <c r="H45" s="1" t="n"/>
@@ -2302,9 +2350,13 @@
           <t>Whey Isolated x 907 gr UT</t>
         </is>
       </c>
-      <c r="C59" s="20" t="n"/>
+      <c r="C59" s="20" t="n">
+        <v>-1</v>
+      </c>
       <c r="D59" s="20" t="n"/>
-      <c r="E59" s="19" t="n"/>
+      <c r="E59" s="19" t="n">
+        <v>-1</v>
+      </c>
       <c r="F59" s="1" t="n"/>
       <c r="G59" s="1" t="n"/>
       <c r="H59" s="1" t="n"/>
@@ -2477,9 +2529,13 @@
           <t>WHEY PROTEIN X 907 GR ULTRA TECH CHOCOLATE</t>
         </is>
       </c>
-      <c r="C66" s="20" t="n"/>
+      <c r="C66" s="20" t="n">
+        <v>-23</v>
+      </c>
       <c r="D66" s="20" t="n"/>
-      <c r="E66" s="19" t="n"/>
+      <c r="E66" s="19" t="n">
+        <v>-23</v>
+      </c>
       <c r="F66" s="1" t="n"/>
       <c r="G66" s="1" t="n"/>
       <c r="H66" s="1" t="n"/>
@@ -2502,9 +2558,13 @@
           <t xml:space="preserve">Whey Protein 907 g.  Vainilla    UT            </t>
         </is>
       </c>
-      <c r="C67" s="20" t="n"/>
+      <c r="C67" s="20" t="n">
+        <v>-20</v>
+      </c>
       <c r="D67" s="20" t="n"/>
-      <c r="E67" s="19" t="n"/>
+      <c r="E67" s="19" t="n">
+        <v>-20</v>
+      </c>
       <c r="F67" s="1" t="n"/>
       <c r="G67" s="1" t="n"/>
       <c r="H67" s="1" t="n"/>
@@ -2577,9 +2637,13 @@
           <t>WHEY PROTEIN X 907 GR ULTRA TECH DULCE DE LECHE</t>
         </is>
       </c>
-      <c r="C70" s="20" t="n"/>
+      <c r="C70" s="20" t="n">
+        <v>-5</v>
+      </c>
       <c r="D70" s="20" t="n"/>
-      <c r="E70" s="19" t="n"/>
+      <c r="E70" s="19" t="n">
+        <v>-5</v>
+      </c>
       <c r="F70" s="1" t="n"/>
       <c r="G70" s="1" t="n"/>
       <c r="H70" s="1" t="n"/>
@@ -2627,9 +2691,13 @@
           <t xml:space="preserve">Ultra Whey Pro 454 g (1 libra)  Vainilla    UT           </t>
         </is>
       </c>
-      <c r="C72" s="18" t="n"/>
+      <c r="C72" s="18" t="n">
+        <v>-37</v>
+      </c>
       <c r="D72" s="18" t="n"/>
-      <c r="E72" s="19" t="n"/>
+      <c r="E72" s="19" t="n">
+        <v>-37</v>
+      </c>
       <c r="F72" s="1" t="n"/>
       <c r="G72" s="1" t="n"/>
       <c r="H72" s="1" t="n"/>
@@ -2652,9 +2720,13 @@
           <t xml:space="preserve">Ultra Whey Pro 454 g (1 libra)  Chocolate     UT      </t>
         </is>
       </c>
-      <c r="C73" s="18" t="n"/>
+      <c r="C73" s="18" t="n">
+        <v>-36</v>
+      </c>
       <c r="D73" s="18" t="n"/>
-      <c r="E73" s="19" t="n"/>
+      <c r="E73" s="19" t="n">
+        <v>-36</v>
+      </c>
       <c r="F73" s="1" t="n"/>
       <c r="G73" s="1" t="n"/>
       <c r="H73" s="1" t="n"/>
@@ -2677,9 +2749,13 @@
           <t>Ultra Whey Pro 454 g (1 libra)  Frutilla    UT</t>
         </is>
       </c>
-      <c r="C74" s="18" t="n"/>
+      <c r="C74" s="18" t="n">
+        <v>-27</v>
+      </c>
       <c r="D74" s="18" t="n"/>
-      <c r="E74" s="19" t="n"/>
+      <c r="E74" s="19" t="n">
+        <v>-27</v>
+      </c>
       <c r="F74" s="1" t="n"/>
       <c r="G74" s="1" t="n"/>
       <c r="H74" s="1" t="n"/>
@@ -2902,9 +2978,13 @@
           <t>3 in 1 Fat Burner System UT</t>
         </is>
       </c>
-      <c r="C83" s="18" t="n"/>
+      <c r="C83" s="18" t="n">
+        <v>-1</v>
+      </c>
       <c r="D83" s="18" t="n"/>
-      <c r="E83" s="19" t="n"/>
+      <c r="E83" s="19" t="n">
+        <v>-1</v>
+      </c>
       <c r="F83" s="1" t="n"/>
       <c r="G83" s="1" t="n"/>
       <c r="H83" s="1" t="n"/>
@@ -3273,9 +3353,13 @@
           <t>Whey Nitro NO2 907 gr      Vainilla UT</t>
         </is>
       </c>
-      <c r="C98" s="18" t="n"/>
+      <c r="C98" s="18" t="n">
+        <v>-1</v>
+      </c>
       <c r="D98" s="18" t="n"/>
-      <c r="E98" s="19" t="n"/>
+      <c r="E98" s="19" t="n">
+        <v>-1</v>
+      </c>
       <c r="F98" s="1" t="n"/>
       <c r="G98" s="1" t="n"/>
       <c r="H98" s="1" t="n"/>
@@ -3469,9 +3553,13 @@
           <t>Protein Bar x 50 gr banana</t>
         </is>
       </c>
-      <c r="C106" s="18" t="n"/>
+      <c r="C106" s="18" t="n">
+        <v>-32</v>
+      </c>
       <c r="D106" s="18" t="n"/>
-      <c r="E106" s="19" t="n"/>
+      <c r="E106" s="19" t="n">
+        <v>-32</v>
+      </c>
       <c r="F106" s="1" t="n"/>
       <c r="G106" s="1" t="n"/>
       <c r="H106" s="1" t="n"/>
@@ -3494,9 +3582,13 @@
           <t>Protein Bar x 50 gr frutilla y yogurt</t>
         </is>
       </c>
-      <c r="C107" s="20" t="n"/>
+      <c r="C107" s="20" t="n">
+        <v>-74</v>
+      </c>
       <c r="D107" s="20" t="n"/>
-      <c r="E107" s="19" t="n"/>
+      <c r="E107" s="19" t="n">
+        <v>-74</v>
+      </c>
       <c r="F107" s="1" t="n"/>
       <c r="G107" s="1" t="n"/>
       <c r="H107" s="1" t="n"/>
@@ -3669,9 +3761,13 @@
           <t>DUBAI BAR</t>
         </is>
       </c>
-      <c r="C114" s="18" t="n"/>
+      <c r="C114" s="18" t="n">
+        <v>-49</v>
+      </c>
       <c r="D114" s="18" t="n"/>
-      <c r="E114" s="19" t="n"/>
+      <c r="E114" s="19" t="n">
+        <v>-49</v>
+      </c>
       <c r="F114" s="1" t="n"/>
       <c r="G114" s="1" t="n"/>
       <c r="H114" s="1" t="n"/>
@@ -3742,9 +3838,13 @@
           <t>ENERGY GEL FRUTOS ROJOS ULTRA TECH CAJA X 12 UNIDADES</t>
         </is>
       </c>
-      <c r="C117" s="20" t="n"/>
+      <c r="C117" s="20" t="n">
+        <v>-15</v>
+      </c>
       <c r="D117" s="20" t="n"/>
-      <c r="E117" s="19" t="n"/>
+      <c r="E117" s="19" t="n">
+        <v>-15</v>
+      </c>
       <c r="F117" s="1" t="n"/>
       <c r="G117" s="1" t="n"/>
       <c r="H117" s="1" t="n"/>
@@ -3792,9 +3892,13 @@
           <t>Energy Gel con Cafeína x 32 g - Sabor árandano x 12 unidades</t>
         </is>
       </c>
-      <c r="C119" s="18" t="n"/>
+      <c r="C119" s="18" t="n">
+        <v>-2</v>
+      </c>
       <c r="D119" s="18" t="n"/>
-      <c r="E119" s="19" t="n"/>
+      <c r="E119" s="19" t="n">
+        <v>-2</v>
+      </c>
       <c r="F119" s="1" t="n"/>
       <c r="G119" s="1" t="n"/>
       <c r="H119" s="1" t="n"/>
@@ -4413,9 +4517,13 @@
           <t>VASO TAPA A ROSCA ULTRA TECH</t>
         </is>
       </c>
-      <c r="C144" s="20" t="n"/>
+      <c r="C144" s="20" t="n">
+        <v>-18</v>
+      </c>
       <c r="D144" s="20" t="n"/>
-      <c r="E144" s="19" t="n"/>
+      <c r="E144" s="19" t="n">
+        <v>-18</v>
+      </c>
       <c r="F144" s="1" t="n"/>
       <c r="G144" s="1" t="n"/>
       <c r="H144" s="1" t="n"/>
@@ -4513,9 +4621,13 @@
           <t>Shaker Eat - shaker 1</t>
         </is>
       </c>
-      <c r="C148" s="18" t="n"/>
+      <c r="C148" s="18" t="n">
+        <v>-9</v>
+      </c>
       <c r="D148" s="18" t="n"/>
-      <c r="E148" s="19" t="n"/>
+      <c r="E148" s="19" t="n">
+        <v>-9</v>
+      </c>
       <c r="F148" s="1" t="n"/>
       <c r="G148" s="1" t="n"/>
       <c r="H148" s="1" t="n"/>
@@ -4711,9 +4823,13 @@
           <t xml:space="preserve">Aceite de pescado + Hig. De Bacalao + Chia x 30 compr. </t>
         </is>
       </c>
-      <c r="C156" s="18" t="n"/>
+      <c r="C156" s="18" t="n">
+        <v>-12</v>
+      </c>
       <c r="D156" s="18" t="n"/>
-      <c r="E156" s="19" t="n"/>
+      <c r="E156" s="19" t="n">
+        <v>-12</v>
+      </c>
       <c r="F156" s="1" t="n"/>
       <c r="G156" s="1" t="n"/>
       <c r="H156" s="1" t="n"/>
@@ -4859,9 +4975,13 @@
           <t>Arginina x 30  VT</t>
         </is>
       </c>
-      <c r="C162" s="18" t="n"/>
+      <c r="C162" s="18" t="n">
+        <v>-16</v>
+      </c>
       <c r="D162" s="18" t="n"/>
-      <c r="E162" s="19" t="n"/>
+      <c r="E162" s="19" t="n">
+        <v>-16</v>
+      </c>
       <c r="F162" s="1" t="n"/>
       <c r="G162" s="1" t="n"/>
       <c r="H162" s="1" t="n"/>
@@ -4959,9 +5079,13 @@
           <t>ASHWAGANDHA 1300 MG X 60 CAPS</t>
         </is>
       </c>
-      <c r="C166" s="20" t="n"/>
+      <c r="C166" s="20" t="n">
+        <v>-45</v>
+      </c>
       <c r="D166" s="20" t="n"/>
-      <c r="E166" s="19" t="n"/>
+      <c r="E166" s="19" t="n">
+        <v>-45</v>
+      </c>
       <c r="F166" s="1" t="n"/>
       <c r="G166" s="1" t="n"/>
       <c r="H166" s="1" t="n"/>
@@ -4984,9 +5108,13 @@
           <t>BISGLICINATO DE MAGNESIO X 60 CAPS VITATECH</t>
         </is>
       </c>
-      <c r="C167" s="20" t="n"/>
+      <c r="C167" s="20" t="n">
+        <v>-126</v>
+      </c>
       <c r="D167" s="20" t="n"/>
-      <c r="E167" s="19" t="n"/>
+      <c r="E167" s="19" t="n">
+        <v>-126</v>
+      </c>
       <c r="F167" s="1" t="n"/>
       <c r="G167" s="1" t="n"/>
       <c r="H167" s="1" t="n"/>
@@ -5009,9 +5137,13 @@
           <t>BISGLICINATO DE MAGNESIO POLVO LIMON</t>
         </is>
       </c>
-      <c r="C168" s="18" t="n"/>
+      <c r="C168" s="18" t="n">
+        <v>-31</v>
+      </c>
       <c r="D168" s="18" t="n"/>
-      <c r="E168" s="19" t="n"/>
+      <c r="E168" s="19" t="n">
+        <v>-31</v>
+      </c>
       <c r="F168" s="1" t="n"/>
       <c r="G168" s="1" t="n"/>
       <c r="H168" s="1" t="n"/>
@@ -5259,9 +5391,13 @@
           <t xml:space="preserve">CITRATO DE POTASIO </t>
         </is>
       </c>
-      <c r="C178" s="18" t="n"/>
+      <c r="C178" s="18" t="n">
+        <v>-11</v>
+      </c>
       <c r="D178" s="18" t="n"/>
-      <c r="E178" s="19" t="n"/>
+      <c r="E178" s="19" t="n">
+        <v>-11</v>
+      </c>
       <c r="F178" s="1" t="n"/>
       <c r="G178" s="1" t="n"/>
       <c r="H178" s="1" t="n"/>
@@ -5359,9 +5495,13 @@
           <t>Colageno x 60 compr VT</t>
         </is>
       </c>
-      <c r="C182" s="20" t="n"/>
+      <c r="C182" s="20" t="n">
+        <v>-20</v>
+      </c>
       <c r="D182" s="20" t="n"/>
-      <c r="E182" s="19" t="n"/>
+      <c r="E182" s="19" t="n">
+        <v>-20</v>
+      </c>
       <c r="F182" s="1" t="n"/>
       <c r="G182" s="1" t="n"/>
       <c r="H182" s="1" t="n"/>
@@ -5459,9 +5599,13 @@
           <t>COLAGENO DEFENSE</t>
         </is>
       </c>
-      <c r="C186" s="18" t="n"/>
+      <c r="C186" s="18" t="n">
+        <v>-9</v>
+      </c>
       <c r="D186" s="18" t="n"/>
-      <c r="E186" s="19" t="n"/>
+      <c r="E186" s="19" t="n">
+        <v>-9</v>
+      </c>
       <c r="F186" s="1" t="n"/>
       <c r="G186" s="1" t="n"/>
       <c r="H186" s="1" t="n"/>
@@ -5484,9 +5628,13 @@
           <t>PROTEINA DE COLAGENO X 360 GR VITATECH FRUTOS DEL BOSQUE</t>
         </is>
       </c>
-      <c r="C187" s="20" t="n"/>
+      <c r="C187" s="20" t="n">
+        <v>-26</v>
+      </c>
       <c r="D187" s="20" t="n"/>
-      <c r="E187" s="19" t="n"/>
+      <c r="E187" s="19" t="n">
+        <v>-26</v>
+      </c>
       <c r="F187" s="1" t="n"/>
       <c r="G187" s="1" t="n"/>
       <c r="H187" s="1" t="n"/>
@@ -5559,9 +5707,13 @@
           <t>VITAFLEX X 360 GR VITATECH</t>
         </is>
       </c>
-      <c r="C190" s="20" t="n"/>
+      <c r="C190" s="20" t="n">
+        <v>-95</v>
+      </c>
       <c r="D190" s="20" t="n"/>
-      <c r="E190" s="19" t="n"/>
+      <c r="E190" s="19" t="n">
+        <v>-95</v>
+      </c>
       <c r="F190" s="1" t="n"/>
       <c r="G190" s="1" t="n"/>
       <c r="H190" s="1" t="n"/>
@@ -5584,9 +5736,13 @@
           <t>Complejo B x 60 comprimidos VT</t>
         </is>
       </c>
-      <c r="C191" s="20" t="n"/>
+      <c r="C191" s="20" t="n">
+        <v>-25</v>
+      </c>
       <c r="D191" s="20" t="n"/>
-      <c r="E191" s="19" t="n"/>
+      <c r="E191" s="19" t="n">
+        <v>-25</v>
+      </c>
       <c r="F191" s="1" t="n"/>
       <c r="G191" s="1" t="n"/>
       <c r="H191" s="1" t="n"/>
@@ -5709,9 +5865,13 @@
           <t>CURCUMA + PIMIENTA NEGRA Y VITAMINA E X30 CAPS</t>
         </is>
       </c>
-      <c r="C196" s="18" t="n"/>
+      <c r="C196" s="18" t="n">
+        <v>-20</v>
+      </c>
       <c r="D196" s="18" t="n"/>
-      <c r="E196" s="19" t="n"/>
+      <c r="E196" s="19" t="n">
+        <v>-20</v>
+      </c>
       <c r="F196" s="1" t="n"/>
       <c r="G196" s="1" t="n"/>
       <c r="H196" s="1" t="n"/>
@@ -5809,9 +5969,13 @@
           <t>GLUTATION * 30 CAPS</t>
         </is>
       </c>
-      <c r="C200" s="18" t="n"/>
+      <c r="C200" s="18" t="n">
+        <v>-1</v>
+      </c>
       <c r="D200" s="18" t="n"/>
-      <c r="E200" s="19" t="n"/>
+      <c r="E200" s="19" t="n">
+        <v>-1</v>
+      </c>
       <c r="F200" s="1" t="n"/>
       <c r="G200" s="1" t="n"/>
       <c r="H200" s="1" t="n"/>
@@ -5884,9 +6048,13 @@
           <t>Guarana x 60 comp VT</t>
         </is>
       </c>
-      <c r="C203" s="18" t="n"/>
+      <c r="C203" s="18" t="n">
+        <v>-13</v>
+      </c>
       <c r="D203" s="18" t="n"/>
-      <c r="E203" s="19" t="n"/>
+      <c r="E203" s="19" t="n">
+        <v>-13</v>
+      </c>
       <c r="F203" s="1" t="n"/>
       <c r="G203" s="1" t="n"/>
       <c r="H203" s="1" t="n"/>
@@ -5959,9 +6127,13 @@
           <t>Krill   VT</t>
         </is>
       </c>
-      <c r="C206" s="18" t="n"/>
+      <c r="C206" s="18" t="n">
+        <v>-14</v>
+      </c>
       <c r="D206" s="18" t="n"/>
-      <c r="E206" s="19" t="n"/>
+      <c r="E206" s="19" t="n">
+        <v>-14</v>
+      </c>
       <c r="F206" s="1" t="n"/>
       <c r="G206" s="1" t="n"/>
       <c r="H206" s="1" t="n"/>
@@ -6059,9 +6231,13 @@
           <t>Luteina x 30 caps VT</t>
         </is>
       </c>
-      <c r="C210" s="18" t="n"/>
+      <c r="C210" s="18" t="n">
+        <v>-13</v>
+      </c>
       <c r="D210" s="18" t="n"/>
-      <c r="E210" s="19" t="n"/>
+      <c r="E210" s="19" t="n">
+        <v>-13</v>
+      </c>
       <c r="F210" s="1" t="n"/>
       <c r="G210" s="1" t="n"/>
       <c r="H210" s="1" t="n"/>
@@ -6109,9 +6285,13 @@
           <t>MAGNESIO X 30 COMP VITATECH</t>
         </is>
       </c>
-      <c r="C212" s="20" t="n"/>
+      <c r="C212" s="20" t="n">
+        <v>-14</v>
+      </c>
       <c r="D212" s="20" t="n"/>
-      <c r="E212" s="19" t="n"/>
+      <c r="E212" s="19" t="n">
+        <v>-14</v>
+      </c>
       <c r="F212" s="1" t="n"/>
       <c r="G212" s="1" t="n"/>
       <c r="H212" s="1" t="n"/>
@@ -6159,9 +6339,13 @@
           <t>VITATECH CITRATO DE MAGNESIO X 30 CÁPSULAS</t>
         </is>
       </c>
-      <c r="C214" s="20" t="n"/>
+      <c r="C214" s="20" t="n">
+        <v>-87</v>
+      </c>
       <c r="D214" s="20" t="n"/>
-      <c r="E214" s="19" t="n"/>
+      <c r="E214" s="19" t="n">
+        <v>-87</v>
+      </c>
       <c r="F214" s="1" t="n"/>
       <c r="G214" s="1" t="n"/>
       <c r="H214" s="1" t="n"/>
@@ -6184,9 +6368,13 @@
           <t>CITRATO DE MAGNESIO  POLVO ARANDANO</t>
         </is>
       </c>
-      <c r="C215" s="20" t="n"/>
+      <c r="C215" s="20" t="n">
+        <v>-21</v>
+      </c>
       <c r="D215" s="20" t="n"/>
-      <c r="E215" s="19" t="n"/>
+      <c r="E215" s="19" t="n">
+        <v>-21</v>
+      </c>
       <c r="F215" s="1" t="n"/>
       <c r="G215" s="1" t="n"/>
       <c r="H215" s="1" t="n"/>
@@ -6234,9 +6422,13 @@
           <t>MELENA DE LEON X 60 CAPS VITATECH 1000 MG</t>
         </is>
       </c>
-      <c r="C217" s="20" t="n"/>
+      <c r="C217" s="20" t="n">
+        <v>-46</v>
+      </c>
       <c r="D217" s="20" t="n"/>
-      <c r="E217" s="19" t="n"/>
+      <c r="E217" s="19" t="n">
+        <v>-46</v>
+      </c>
       <c r="F217" s="1" t="n"/>
       <c r="G217" s="1" t="n"/>
       <c r="H217" s="1" t="n"/>
@@ -6259,9 +6451,13 @@
           <t>MULTIVITAMINAS Y MINERALES X 60 COMP VITATECH</t>
         </is>
       </c>
-      <c r="C218" s="20" t="n"/>
+      <c r="C218" s="20" t="n">
+        <v>-20</v>
+      </c>
       <c r="D218" s="20" t="n"/>
-      <c r="E218" s="19" t="n"/>
+      <c r="E218" s="19" t="n">
+        <v>-20</v>
+      </c>
       <c r="F218" s="1" t="n"/>
       <c r="G218" s="1" t="n"/>
       <c r="H218" s="1" t="n"/>
@@ -6284,9 +6480,13 @@
           <t xml:space="preserve">Plant Protein bar caja x 12 unidades </t>
         </is>
       </c>
-      <c r="C219" s="18" t="n"/>
+      <c r="C219" s="18" t="n">
+        <v>-18</v>
+      </c>
       <c r="D219" s="18" t="n"/>
-      <c r="E219" s="19" t="n"/>
+      <c r="E219" s="19" t="n">
+        <v>-18</v>
+      </c>
       <c r="F219" s="1" t="n"/>
       <c r="G219" s="1" t="n"/>
       <c r="H219" s="1" t="n"/>
@@ -6309,9 +6509,13 @@
           <t>Potasio - Magnesio x 60 caps</t>
         </is>
       </c>
-      <c r="C220" s="20" t="n"/>
+      <c r="C220" s="20" t="n">
+        <v>-59</v>
+      </c>
       <c r="D220" s="20" t="n"/>
-      <c r="E220" s="19" t="n"/>
+      <c r="E220" s="19" t="n">
+        <v>-59</v>
+      </c>
       <c r="F220" s="1" t="n"/>
       <c r="G220" s="1" t="n"/>
       <c r="H220" s="1" t="n"/>
@@ -6409,9 +6613,13 @@
           <t>RESVERATROL PLUS</t>
         </is>
       </c>
-      <c r="C224" s="18" t="n"/>
+      <c r="C224" s="18" t="n">
+        <v>-20</v>
+      </c>
       <c r="D224" s="18" t="n"/>
-      <c r="E224" s="19" t="n"/>
+      <c r="E224" s="19" t="n">
+        <v>-20</v>
+      </c>
       <c r="F224" s="1" t="n"/>
       <c r="G224" s="1" t="n"/>
       <c r="H224" s="1" t="n"/>
@@ -6559,9 +6767,13 @@
           <t>TREONATO DE MAGNESIO X 60 CAPS VITATECH</t>
         </is>
       </c>
-      <c r="C230" s="20" t="n"/>
+      <c r="C230" s="20" t="n">
+        <v>-20</v>
+      </c>
       <c r="D230" s="20" t="n"/>
-      <c r="E230" s="19" t="n"/>
+      <c r="E230" s="19" t="n">
+        <v>-20</v>
+      </c>
       <c r="F230" s="1" t="n"/>
       <c r="G230" s="1" t="n"/>
       <c r="H230" s="1" t="n"/>
@@ -6584,9 +6796,13 @@
           <t>Vision x 30 comp VT</t>
         </is>
       </c>
-      <c r="C231" s="18" t="n"/>
+      <c r="C231" s="18" t="n">
+        <v>-9</v>
+      </c>
       <c r="D231" s="18" t="n"/>
-      <c r="E231" s="19" t="n"/>
+      <c r="E231" s="19" t="n">
+        <v>-9</v>
+      </c>
       <c r="F231" s="1" t="n"/>
       <c r="G231" s="1" t="n"/>
       <c r="H231" s="1" t="n"/>
@@ -6634,9 +6850,13 @@
           <t>Vita stress x 30</t>
         </is>
       </c>
-      <c r="C233" s="18" t="n"/>
+      <c r="C233" s="18" t="n">
+        <v>-10</v>
+      </c>
       <c r="D233" s="18" t="n"/>
-      <c r="E233" s="19" t="n"/>
+      <c r="E233" s="19" t="n">
+        <v>-10</v>
+      </c>
       <c r="F233" s="1" t="n"/>
       <c r="G233" s="1" t="n"/>
       <c r="H233" s="1" t="n"/>
@@ -6659,9 +6879,13 @@
           <t>Vitamina A  x 30 comp VT</t>
         </is>
       </c>
-      <c r="C234" s="18" t="n"/>
+      <c r="C234" s="18" t="n">
+        <v>-3</v>
+      </c>
       <c r="D234" s="18" t="n"/>
-      <c r="E234" s="19" t="n"/>
+      <c r="E234" s="19" t="n">
+        <v>-3</v>
+      </c>
       <c r="F234" s="1" t="n"/>
       <c r="G234" s="1" t="n"/>
       <c r="H234" s="1" t="n"/>
@@ -6684,9 +6908,13 @@
           <t xml:space="preserve"> VITAMINA C X 30 COMP VITATECH</t>
         </is>
       </c>
-      <c r="C235" s="20" t="n"/>
+      <c r="C235" s="20" t="n">
+        <v>-9</v>
+      </c>
       <c r="D235" s="20" t="n"/>
-      <c r="E235" s="19" t="n"/>
+      <c r="E235" s="19" t="n">
+        <v>-9</v>
+      </c>
       <c r="F235" s="1" t="n"/>
       <c r="G235" s="1" t="n"/>
       <c r="H235" s="1" t="n"/>
@@ -6809,9 +7037,13 @@
           <t>ZINC X 30 COMP VITATECH</t>
         </is>
       </c>
-      <c r="C240" s="20" t="n"/>
+      <c r="C240" s="20" t="n">
+        <v>-82</v>
+      </c>
       <c r="D240" s="20" t="n"/>
-      <c r="E240" s="19" t="n"/>
+      <c r="E240" s="19" t="n">
+        <v>-82</v>
+      </c>
       <c r="F240" s="1" t="n"/>
       <c r="G240" s="1" t="n"/>
       <c r="H240" s="1" t="n"/>
@@ -6834,9 +7066,13 @@
           <t>ZINC QUELATO</t>
         </is>
       </c>
-      <c r="C241" s="18" t="n"/>
+      <c r="C241" s="18" t="n">
+        <v>-6</v>
+      </c>
       <c r="D241" s="18" t="n"/>
-      <c r="E241" s="19" t="n"/>
+      <c r="E241" s="19" t="n">
+        <v>-6</v>
+      </c>
       <c r="F241" s="1" t="n"/>
       <c r="G241" s="1" t="n"/>
       <c r="H241" s="1" t="n"/>
@@ -6859,9 +7095,13 @@
           <t>VITAMINA K2 X 30 COMP VITATECH</t>
         </is>
       </c>
-      <c r="C242" s="20" t="n"/>
+      <c r="C242" s="20" t="n">
+        <v>-61</v>
+      </c>
       <c r="D242" s="20" t="n"/>
-      <c r="E242" s="19" t="n"/>
+      <c r="E242" s="19" t="n">
+        <v>-61</v>
+      </c>
       <c r="F242" s="1" t="n"/>
       <c r="G242" s="1" t="n"/>
       <c r="H242" s="1" t="n"/>
@@ -6934,9 +7174,13 @@
           <t>NAD+ VITATECH X 60 CAPSULAS</t>
         </is>
       </c>
-      <c r="C245" s="20" t="n"/>
+      <c r="C245" s="20" t="n">
+        <v>-142</v>
+      </c>
       <c r="D245" s="20" t="n"/>
-      <c r="E245" s="19" t="n"/>
+      <c r="E245" s="19" t="n">
+        <v>-142</v>
+      </c>
       <c r="F245" s="1" t="n"/>
       <c r="G245" s="1" t="n"/>
       <c r="H245" s="1" t="n"/>
@@ -6959,9 +7203,13 @@
           <t>NAD+ TESTO HOMBRE</t>
         </is>
       </c>
-      <c r="C246" s="20" t="n"/>
+      <c r="C246" s="20" t="n">
+        <v>-34</v>
+      </c>
       <c r="D246" s="20" t="n"/>
-      <c r="E246" s="19" t="n"/>
+      <c r="E246" s="19" t="n">
+        <v>-34</v>
+      </c>
       <c r="F246" s="1" t="n"/>
       <c r="G246" s="1" t="n"/>
       <c r="H246" s="1" t="n"/>
@@ -6984,9 +7232,13 @@
           <t>NAD EN POLVO X 348 GRS</t>
         </is>
       </c>
-      <c r="C247" s="18" t="n"/>
+      <c r="C247" s="18" t="n">
+        <v>-61</v>
+      </c>
       <c r="D247" s="18" t="n"/>
-      <c r="E247" s="19" t="n"/>
+      <c r="E247" s="19" t="n">
+        <v>-61</v>
+      </c>
       <c r="F247" s="1" t="n"/>
       <c r="G247" s="1" t="n"/>
       <c r="H247" s="1" t="n"/>
@@ -7278,9 +7530,13 @@
           <t>Protein Bar Mini 25 gr x 24 unidades</t>
         </is>
       </c>
-      <c r="C259" s="18" t="n"/>
+      <c r="C259" s="18" t="n">
+        <v>-15</v>
+      </c>
       <c r="D259" s="18" t="n"/>
-      <c r="E259" s="19" t="n"/>
+      <c r="E259" s="19" t="n">
+        <v>-15</v>
+      </c>
       <c r="F259" s="1" t="n"/>
       <c r="G259" s="1" t="n"/>
       <c r="H259" s="1" t="n"/>
@@ -7303,9 +7559,13 @@
           <t>PROTEIN BAR SUGAR FREE X 12 UNIDADES PROTEIN FACTORY DULCE DE LECHE</t>
         </is>
       </c>
-      <c r="C260" s="20" t="n"/>
+      <c r="C260" s="20" t="n">
+        <v>-222</v>
+      </c>
       <c r="D260" s="20" t="n"/>
-      <c r="E260" s="19" t="n"/>
+      <c r="E260" s="19" t="n">
+        <v>-222</v>
+      </c>
       <c r="F260" s="1" t="n"/>
       <c r="G260" s="1" t="n"/>
       <c r="H260" s="1" t="n"/>
@@ -7328,9 +7588,13 @@
           <t>Protein Bar Sugar Free x 46 gr Chocolate</t>
         </is>
       </c>
-      <c r="C261" s="18" t="n"/>
+      <c r="C261" s="18" t="n">
+        <v>-58</v>
+      </c>
       <c r="D261" s="18" t="n"/>
-      <c r="E261" s="19" t="n"/>
+      <c r="E261" s="19" t="n">
+        <v>-58</v>
+      </c>
       <c r="F261" s="1" t="n"/>
       <c r="G261" s="1" t="n"/>
       <c r="H261" s="1" t="n"/>
@@ -7376,9 +7640,13 @@
           <t>PROTEIN PANCAKE DOYPACK PROTEIN FACTORY</t>
         </is>
       </c>
-      <c r="C263" s="20" t="n"/>
+      <c r="C263" s="20" t="n">
+        <v>-55</v>
+      </c>
       <c r="D263" s="20" t="n"/>
-      <c r="E263" s="19" t="n"/>
+      <c r="E263" s="19" t="n">
+        <v>-55</v>
+      </c>
       <c r="F263" s="1" t="n"/>
       <c r="G263" s="1" t="n"/>
       <c r="H263" s="1" t="n"/>
@@ -7426,9 +7694,13 @@
           <t xml:space="preserve">Protein Cafe Latte x 240 grs </t>
         </is>
       </c>
-      <c r="C265" s="18" t="n"/>
+      <c r="C265" s="18" t="n">
+        <v>-33</v>
+      </c>
       <c r="D265" s="18" t="n"/>
-      <c r="E265" s="19" t="n"/>
+      <c r="E265" s="19" t="n">
+        <v>-33</v>
+      </c>
       <c r="F265" s="1" t="n"/>
       <c r="G265" s="1" t="n"/>
       <c r="H265" s="1" t="n"/>
@@ -7451,9 +7723,13 @@
           <t xml:space="preserve">Protein Omelette x 240 grs </t>
         </is>
       </c>
-      <c r="C266" s="20" t="n"/>
+      <c r="C266" s="20" t="n">
+        <v>-9</v>
+      </c>
       <c r="D266" s="20" t="n"/>
-      <c r="E266" s="19" t="n"/>
+      <c r="E266" s="19" t="n">
+        <v>-9</v>
+      </c>
       <c r="F266" s="1" t="n"/>
       <c r="G266" s="1" t="n"/>
       <c r="H266" s="1" t="n"/>
@@ -7549,9 +7825,13 @@
           <t>Xing Yu x 4 caps</t>
         </is>
       </c>
-      <c r="C270" s="18" t="n"/>
+      <c r="C270" s="18" t="n">
+        <v>-130</v>
+      </c>
       <c r="D270" s="18" t="n"/>
-      <c r="E270" s="19" t="n"/>
+      <c r="E270" s="19" t="n">
+        <v>-130</v>
+      </c>
       <c r="F270" s="1" t="n"/>
       <c r="G270" s="1" t="n"/>
       <c r="H270" s="1" t="n"/>
@@ -7574,9 +7854,13 @@
           <t>Xing Yu x 8 caps</t>
         </is>
       </c>
-      <c r="C271" s="18" t="n"/>
+      <c r="C271" s="18" t="n">
+        <v>-36</v>
+      </c>
       <c r="D271" s="18" t="n"/>
-      <c r="E271" s="19" t="n"/>
+      <c r="E271" s="19" t="n">
+        <v>-36</v>
+      </c>
       <c r="F271" s="1" t="n"/>
       <c r="G271" s="1" t="n"/>
       <c r="H271" s="1" t="n"/>
@@ -7599,9 +7883,13 @@
           <t>ULTRA MUJER</t>
         </is>
       </c>
-      <c r="C272" s="35" t="n"/>
+      <c r="C272" s="35" t="n">
+        <v>-207</v>
+      </c>
       <c r="D272" s="35" t="n"/>
-      <c r="E272" s="19" t="n"/>
+      <c r="E272" s="19" t="n">
+        <v>-207</v>
+      </c>
       <c r="F272" s="1" t="n"/>
       <c r="G272" s="1" t="n"/>
       <c r="H272" s="1" t="n"/>
@@ -7624,9 +7912,13 @@
           <t>ULTRA HOMBRE</t>
         </is>
       </c>
-      <c r="C273" s="35" t="n"/>
+      <c r="C273" s="35" t="n">
+        <v>-40</v>
+      </c>
       <c r="D273" s="35" t="n"/>
-      <c r="E273" s="19" t="n"/>
+      <c r="E273" s="19" t="n">
+        <v>-40</v>
+      </c>
       <c r="F273" s="1" t="n"/>
       <c r="G273" s="1" t="n"/>
       <c r="H273" s="1" t="n"/>
@@ -8102,9 +8394,13 @@
           <t>EXHIBIDOR MOSTRADOR BARRAS ULTRA TECH (DOBLE)</t>
         </is>
       </c>
-      <c r="C293" s="35" t="n"/>
+      <c r="C293" s="35" t="n">
+        <v>-3</v>
+      </c>
       <c r="D293" s="35" t="n"/>
-      <c r="E293" s="19" t="n"/>
+      <c r="E293" s="19" t="n">
+        <v>-3</v>
+      </c>
       <c r="F293" s="1" t="n"/>
       <c r="G293" s="1" t="n"/>
       <c r="H293" s="1" t="n"/>
@@ -8187,9 +8483,13 @@
           <t>FOLLETOS ULTRA TECH - PACK X 15 FOLLETOS</t>
         </is>
       </c>
-      <c r="C296" s="38" t="n"/>
+      <c r="C296" s="38" t="n">
+        <v>-12</v>
+      </c>
       <c r="D296" s="38" t="n"/>
-      <c r="E296" s="19" t="n"/>
+      <c r="E296" s="19" t="n">
+        <v>-12</v>
+      </c>
       <c r="F296" s="1" t="n"/>
       <c r="G296" s="1" t="n"/>
       <c r="H296" s="1" t="n"/>
@@ -8222,9 +8522,13 @@
           <t xml:space="preserve">FOLLETOS GELES </t>
         </is>
       </c>
-      <c r="C297" s="38" t="n"/>
+      <c r="C297" s="38" t="n">
+        <v>-1</v>
+      </c>
       <c r="D297" s="38" t="n"/>
-      <c r="E297" s="19" t="n"/>
+      <c r="E297" s="19" t="n">
+        <v>-1</v>
+      </c>
       <c r="F297" s="1" t="n"/>
       <c r="G297" s="1" t="n"/>
       <c r="H297" s="1" t="n"/>
@@ -8600,9 +8904,13 @@
           <t>FOLLETOS VITATECH - PACK X 15 FOLLETOS</t>
         </is>
       </c>
-      <c r="C311" s="38" t="n"/>
+      <c r="C311" s="38" t="n">
+        <v>-15</v>
+      </c>
       <c r="D311" s="38" t="n"/>
-      <c r="E311" s="19" t="n"/>
+      <c r="E311" s="19" t="n">
+        <v>-15</v>
+      </c>
       <c r="F311" s="1" t="n"/>
       <c r="G311" s="1" t="n"/>
       <c r="H311" s="1" t="n"/>
@@ -9116,9 +9424,13 @@
           <t>DUBAI protein bar x unidad</t>
         </is>
       </c>
-      <c r="C333" s="35" t="n"/>
+      <c r="C333" s="35" t="n">
+        <v>-15</v>
+      </c>
       <c r="D333" s="35" t="n"/>
-      <c r="E333" s="19" t="n"/>
+      <c r="E333" s="19" t="n">
+        <v>-15</v>
+      </c>
       <c r="F333" s="1" t="n"/>
       <c r="G333" s="1" t="n"/>
       <c r="H333" s="1" t="n"/>
@@ -9166,9 +9478,13 @@
           <t>Protein Bar - 50 g banana x unidad</t>
         </is>
       </c>
-      <c r="C335" s="35" t="n"/>
+      <c r="C335" s="35" t="n">
+        <v>-2</v>
+      </c>
       <c r="D335" s="35" t="n"/>
-      <c r="E335" s="19" t="n"/>
+      <c r="E335" s="19" t="n">
+        <v>-2</v>
+      </c>
       <c r="F335" s="1" t="n"/>
       <c r="G335" s="1" t="n"/>
       <c r="H335" s="1" t="n"/>
@@ -9191,9 +9507,13 @@
           <t>Protein Bar - 50 g frutilla con yogurt x unidad</t>
         </is>
       </c>
-      <c r="C336" s="35" t="n"/>
+      <c r="C336" s="35" t="n">
+        <v>-2</v>
+      </c>
       <c r="D336" s="35" t="n"/>
-      <c r="E336" s="19" t="n"/>
+      <c r="E336" s="19" t="n">
+        <v>-2</v>
+      </c>
       <c r="F336" s="1" t="n"/>
       <c r="G336" s="1" t="n"/>
       <c r="H336" s="1" t="n"/>
@@ -9766,9 +10086,13 @@
           <t>Protein Bar - 50 g banana x unidad</t>
         </is>
       </c>
-      <c r="C359" s="35" t="n"/>
+      <c r="C359" s="35" t="n">
+        <v>-2</v>
+      </c>
       <c r="D359" s="35" t="n"/>
-      <c r="E359" s="19" t="n"/>
+      <c r="E359" s="19" t="n">
+        <v>-2</v>
+      </c>
       <c r="F359" s="1" t="n"/>
       <c r="G359" s="1" t="n"/>
       <c r="H359" s="1" t="n"/>
@@ -9791,9 +10115,13 @@
           <t>Protein Bar - 50 g frutilla con yogurt x unidad</t>
         </is>
       </c>
-      <c r="C360" s="35" t="n"/>
+      <c r="C360" s="35" t="n">
+        <v>-2</v>
+      </c>
       <c r="D360" s="35" t="n"/>
-      <c r="E360" s="19" t="n"/>
+      <c r="E360" s="19" t="n">
+        <v>-2</v>
+      </c>
       <c r="F360" s="1" t="n"/>
       <c r="G360" s="1" t="n"/>
       <c r="H360" s="1" t="n"/>
@@ -9816,9 +10144,13 @@
           <t>Protein bar café x unidad</t>
         </is>
       </c>
-      <c r="C361" s="35" t="n"/>
+      <c r="C361" s="35" t="n">
+        <v>-2</v>
+      </c>
       <c r="D361" s="35" t="n"/>
-      <c r="E361" s="19" t="n"/>
+      <c r="E361" s="19" t="n">
+        <v>-2</v>
+      </c>
       <c r="F361" s="1" t="n"/>
       <c r="G361" s="1" t="n"/>
       <c r="H361" s="1" t="n"/>
@@ -9891,9 +10223,13 @@
           <t>DUBAI protein bar x unidad</t>
         </is>
       </c>
-      <c r="C364" s="35" t="n"/>
+      <c r="C364" s="35" t="n">
+        <v>-15</v>
+      </c>
       <c r="D364" s="35" t="n"/>
-      <c r="E364" s="19" t="n"/>
+      <c r="E364" s="19" t="n">
+        <v>-15</v>
+      </c>
       <c r="F364" s="1" t="n"/>
       <c r="G364" s="1" t="n"/>
       <c r="H364" s="1" t="n"/>
@@ -9941,9 +10277,13 @@
           <t>Protein Bar - 50 g banana x unidad</t>
         </is>
       </c>
-      <c r="C366" s="35" t="n"/>
+      <c r="C366" s="35" t="n">
+        <v>-2</v>
+      </c>
       <c r="D366" s="35" t="n"/>
-      <c r="E366" s="19" t="n"/>
+      <c r="E366" s="19" t="n">
+        <v>-2</v>
+      </c>
       <c r="F366" s="1" t="n"/>
       <c r="G366" s="1" t="n"/>
       <c r="H366" s="1" t="n"/>
@@ -9966,9 +10306,13 @@
           <t>Protein Bar - 50 g frutilla con yogurt x unidad</t>
         </is>
       </c>
-      <c r="C367" s="35" t="n"/>
+      <c r="C367" s="35" t="n">
+        <v>-2</v>
+      </c>
       <c r="D367" s="35" t="n"/>
-      <c r="E367" s="19" t="n"/>
+      <c r="E367" s="19" t="n">
+        <v>-2</v>
+      </c>
       <c r="F367" s="1" t="n"/>
       <c r="G367" s="1" t="n"/>
       <c r="H367" s="1" t="n"/>
@@ -9991,9 +10335,13 @@
           <t>Protein bar café x unidad</t>
         </is>
       </c>
-      <c r="C368" s="35" t="n"/>
+      <c r="C368" s="35" t="n">
+        <v>-2</v>
+      </c>
       <c r="D368" s="35" t="n"/>
-      <c r="E368" s="19" t="n"/>
+      <c r="E368" s="19" t="n">
+        <v>-2</v>
+      </c>
       <c r="F368" s="1" t="n"/>
       <c r="G368" s="1" t="n"/>
       <c r="H368" s="1" t="n"/>

--- a/Descuentos/Productos_backup.xlsx
+++ b/Descuentos/Productos_backup.xlsx
@@ -1023,13 +1023,9 @@
           <t>Beta Alanine</t>
         </is>
       </c>
-      <c r="C8" s="18" t="n">
-        <v>-2</v>
-      </c>
+      <c r="C8" s="18" t="n"/>
       <c r="D8" s="18" t="n"/>
-      <c r="E8" s="19" t="n">
-        <v>-2</v>
-      </c>
+      <c r="E8" s="19" t="n"/>
       <c r="F8" s="1" t="n"/>
       <c r="G8" s="1" t="n"/>
       <c r="H8" s="1" t="n"/>
@@ -1152,13 +1148,9 @@
           <t>CITRATO MAGNESIO  * 60 UT</t>
         </is>
       </c>
-      <c r="C13" s="18" t="n">
-        <v>-17</v>
-      </c>
+      <c r="C13" s="18" t="n"/>
       <c r="D13" s="18" t="n"/>
-      <c r="E13" s="19" t="n">
-        <v>-17</v>
-      </c>
+      <c r="E13" s="19" t="n"/>
       <c r="F13" s="1" t="n"/>
       <c r="G13" s="1" t="n"/>
       <c r="H13" s="1" t="n"/>
@@ -1231,13 +1223,9 @@
           <t>CREATINA EN COMPRIMIDOS ULTRA TECH</t>
         </is>
       </c>
-      <c r="C16" s="20" t="n">
-        <v>-30</v>
-      </c>
+      <c r="C16" s="20" t="n"/>
       <c r="D16" s="20" t="n"/>
-      <c r="E16" s="19" t="n">
-        <v>-30</v>
-      </c>
+      <c r="E16" s="19" t="n"/>
       <c r="F16" s="1" t="n"/>
       <c r="G16" s="1" t="n"/>
       <c r="H16" s="1" t="n"/>
@@ -1261,11 +1249,11 @@
         </is>
       </c>
       <c r="C17" s="20" t="n">
-        <v>-21</v>
+        <v>25</v>
       </c>
       <c r="D17" s="20" t="n"/>
       <c r="E17" s="19" t="n">
-        <v>-21</v>
+        <v>25</v>
       </c>
       <c r="F17" s="1" t="n"/>
       <c r="G17" s="1" t="n"/>
@@ -1290,11 +1278,11 @@
         </is>
       </c>
       <c r="C18" s="20" t="n">
-        <v>-79</v>
+        <v>50</v>
       </c>
       <c r="D18" s="20" t="n"/>
       <c r="E18" s="19" t="n">
-        <v>-79</v>
+        <v>50</v>
       </c>
       <c r="F18" s="1" t="n"/>
       <c r="G18" s="1" t="n"/>
@@ -1318,13 +1306,9 @@
           <t>Creatine 500 g UT</t>
         </is>
       </c>
-      <c r="C19" s="20" t="n">
-        <v>-23</v>
-      </c>
+      <c r="C19" s="20" t="n"/>
       <c r="D19" s="20" t="n"/>
-      <c r="E19" s="19" t="n">
-        <v>-23</v>
-      </c>
+      <c r="E19" s="19" t="n"/>
       <c r="F19" s="1" t="n"/>
       <c r="G19" s="1" t="n"/>
       <c r="H19" s="1" t="n"/>
@@ -1397,13 +1381,9 @@
           <t>SABORIZADA CREATINA 300 G ULTRA TECH FRUTOS ROJOS C/ LIMON</t>
         </is>
       </c>
-      <c r="C22" s="20" t="n">
-        <v>-28</v>
-      </c>
+      <c r="C22" s="20" t="n"/>
       <c r="D22" s="20" t="n"/>
-      <c r="E22" s="19" t="n">
-        <v>-28</v>
-      </c>
+      <c r="E22" s="19" t="n"/>
       <c r="F22" s="1" t="n"/>
       <c r="G22" s="1" t="n"/>
       <c r="H22" s="1" t="n"/>
@@ -1676,13 +1656,9 @@
           <t>FAT BURNER FOR MEN X 60 CAPS ULTRA TECH</t>
         </is>
       </c>
-      <c r="C33" s="20" t="n">
-        <v>-7</v>
-      </c>
+      <c r="C33" s="20" t="n"/>
       <c r="D33" s="20" t="n"/>
-      <c r="E33" s="19" t="n">
-        <v>-7</v>
-      </c>
+      <c r="E33" s="19" t="n"/>
       <c r="F33" s="1" t="n"/>
       <c r="G33" s="1" t="n"/>
       <c r="H33" s="1" t="n"/>
@@ -1705,13 +1681,9 @@
           <t>FAT BURNER WOMEN X 60 CAPS ULTRA TECH</t>
         </is>
       </c>
-      <c r="C34" s="20" t="n">
-        <v>-52</v>
-      </c>
+      <c r="C34" s="20" t="n"/>
       <c r="D34" s="20" t="n"/>
-      <c r="E34" s="19" t="n">
-        <v>-52</v>
-      </c>
+      <c r="E34" s="19" t="n"/>
       <c r="F34" s="1" t="n"/>
       <c r="G34" s="1" t="n"/>
       <c r="H34" s="1" t="n"/>
@@ -1859,13 +1831,9 @@
           <t xml:space="preserve">Lipo stack UT </t>
         </is>
       </c>
-      <c r="C40" s="18" t="n">
-        <v>-2</v>
-      </c>
+      <c r="C40" s="18" t="n"/>
       <c r="D40" s="18" t="n"/>
-      <c r="E40" s="19" t="n">
-        <v>-2</v>
-      </c>
+      <c r="E40" s="19" t="n"/>
       <c r="F40" s="1" t="n"/>
       <c r="G40" s="1" t="n"/>
       <c r="H40" s="1" t="n"/>
@@ -1938,13 +1906,9 @@
           <t>MAGNESIO TRIPLE * 180GR LIMON UT</t>
         </is>
       </c>
-      <c r="C43" s="18" t="n">
-        <v>-21</v>
-      </c>
+      <c r="C43" s="18" t="n"/>
       <c r="D43" s="18" t="n"/>
-      <c r="E43" s="19" t="n">
-        <v>-21</v>
-      </c>
+      <c r="E43" s="19" t="n"/>
       <c r="F43" s="1" t="n"/>
       <c r="G43" s="1" t="n"/>
       <c r="H43" s="1" t="n"/>
@@ -1967,13 +1931,9 @@
           <t>MULTI COLLAGEN X 405 GR ULTRA TECH</t>
         </is>
       </c>
-      <c r="C44" s="20" t="n">
-        <v>-7</v>
-      </c>
+      <c r="C44" s="20" t="n"/>
       <c r="D44" s="20" t="n"/>
-      <c r="E44" s="19" t="n">
-        <v>-7</v>
-      </c>
+      <c r="E44" s="19" t="n"/>
       <c r="F44" s="1" t="n"/>
       <c r="G44" s="1" t="n"/>
       <c r="H44" s="1" t="n"/>
@@ -1996,13 +1956,9 @@
           <t>Multivitaminas y minerales con ginseng UT</t>
         </is>
       </c>
-      <c r="C45" s="20" t="n">
-        <v>-7</v>
-      </c>
+      <c r="C45" s="20" t="n"/>
       <c r="D45" s="20" t="n"/>
-      <c r="E45" s="19" t="n">
-        <v>-7</v>
-      </c>
+      <c r="E45" s="19" t="n"/>
       <c r="F45" s="1" t="n"/>
       <c r="G45" s="1" t="n"/>
       <c r="H45" s="1" t="n"/>
@@ -2350,13 +2306,9 @@
           <t>Whey Isolated x 907 gr UT</t>
         </is>
       </c>
-      <c r="C59" s="20" t="n">
-        <v>-1</v>
-      </c>
+      <c r="C59" s="20" t="n"/>
       <c r="D59" s="20" t="n"/>
-      <c r="E59" s="19" t="n">
-        <v>-1</v>
-      </c>
+      <c r="E59" s="19" t="n"/>
       <c r="F59" s="1" t="n"/>
       <c r="G59" s="1" t="n"/>
       <c r="H59" s="1" t="n"/>
@@ -2529,13 +2481,9 @@
           <t>WHEY PROTEIN X 907 GR ULTRA TECH CHOCOLATE</t>
         </is>
       </c>
-      <c r="C66" s="20" t="n">
-        <v>-23</v>
-      </c>
+      <c r="C66" s="20" t="n"/>
       <c r="D66" s="20" t="n"/>
-      <c r="E66" s="19" t="n">
-        <v>-23</v>
-      </c>
+      <c r="E66" s="19" t="n"/>
       <c r="F66" s="1" t="n"/>
       <c r="G66" s="1" t="n"/>
       <c r="H66" s="1" t="n"/>
@@ -2558,13 +2506,9 @@
           <t xml:space="preserve">Whey Protein 907 g.  Vainilla    UT            </t>
         </is>
       </c>
-      <c r="C67" s="20" t="n">
-        <v>-20</v>
-      </c>
+      <c r="C67" s="20" t="n"/>
       <c r="D67" s="20" t="n"/>
-      <c r="E67" s="19" t="n">
-        <v>-20</v>
-      </c>
+      <c r="E67" s="19" t="n"/>
       <c r="F67" s="1" t="n"/>
       <c r="G67" s="1" t="n"/>
       <c r="H67" s="1" t="n"/>
@@ -2637,13 +2581,9 @@
           <t>WHEY PROTEIN X 907 GR ULTRA TECH DULCE DE LECHE</t>
         </is>
       </c>
-      <c r="C70" s="20" t="n">
-        <v>-5</v>
-      </c>
+      <c r="C70" s="20" t="n"/>
       <c r="D70" s="20" t="n"/>
-      <c r="E70" s="19" t="n">
-        <v>-5</v>
-      </c>
+      <c r="E70" s="19" t="n"/>
       <c r="F70" s="1" t="n"/>
       <c r="G70" s="1" t="n"/>
       <c r="H70" s="1" t="n"/>
@@ -2691,13 +2631,9 @@
           <t xml:space="preserve">Ultra Whey Pro 454 g (1 libra)  Vainilla    UT           </t>
         </is>
       </c>
-      <c r="C72" s="18" t="n">
-        <v>-37</v>
-      </c>
+      <c r="C72" s="18" t="n"/>
       <c r="D72" s="18" t="n"/>
-      <c r="E72" s="19" t="n">
-        <v>-37</v>
-      </c>
+      <c r="E72" s="19" t="n"/>
       <c r="F72" s="1" t="n"/>
       <c r="G72" s="1" t="n"/>
       <c r="H72" s="1" t="n"/>
@@ -2720,13 +2656,9 @@
           <t xml:space="preserve">Ultra Whey Pro 454 g (1 libra)  Chocolate     UT      </t>
         </is>
       </c>
-      <c r="C73" s="18" t="n">
-        <v>-36</v>
-      </c>
+      <c r="C73" s="18" t="n"/>
       <c r="D73" s="18" t="n"/>
-      <c r="E73" s="19" t="n">
-        <v>-36</v>
-      </c>
+      <c r="E73" s="19" t="n"/>
       <c r="F73" s="1" t="n"/>
       <c r="G73" s="1" t="n"/>
       <c r="H73" s="1" t="n"/>
@@ -2749,13 +2681,9 @@
           <t>Ultra Whey Pro 454 g (1 libra)  Frutilla    UT</t>
         </is>
       </c>
-      <c r="C74" s="18" t="n">
-        <v>-27</v>
-      </c>
+      <c r="C74" s="18" t="n"/>
       <c r="D74" s="18" t="n"/>
-      <c r="E74" s="19" t="n">
-        <v>-27</v>
-      </c>
+      <c r="E74" s="19" t="n"/>
       <c r="F74" s="1" t="n"/>
       <c r="G74" s="1" t="n"/>
       <c r="H74" s="1" t="n"/>
@@ -2978,13 +2906,9 @@
           <t>3 in 1 Fat Burner System UT</t>
         </is>
       </c>
-      <c r="C83" s="18" t="n">
-        <v>-1</v>
-      </c>
+      <c r="C83" s="18" t="n"/>
       <c r="D83" s="18" t="n"/>
-      <c r="E83" s="19" t="n">
-        <v>-1</v>
-      </c>
+      <c r="E83" s="19" t="n"/>
       <c r="F83" s="1" t="n"/>
       <c r="G83" s="1" t="n"/>
       <c r="H83" s="1" t="n"/>
@@ -3353,13 +3277,9 @@
           <t>Whey Nitro NO2 907 gr      Vainilla UT</t>
         </is>
       </c>
-      <c r="C98" s="18" t="n">
-        <v>-1</v>
-      </c>
+      <c r="C98" s="18" t="n"/>
       <c r="D98" s="18" t="n"/>
-      <c r="E98" s="19" t="n">
-        <v>-1</v>
-      </c>
+      <c r="E98" s="19" t="n"/>
       <c r="F98" s="1" t="n"/>
       <c r="G98" s="1" t="n"/>
       <c r="H98" s="1" t="n"/>
@@ -3553,13 +3473,9 @@
           <t>Protein Bar x 50 gr banana</t>
         </is>
       </c>
-      <c r="C106" s="18" t="n">
-        <v>-32</v>
-      </c>
+      <c r="C106" s="18" t="n"/>
       <c r="D106" s="18" t="n"/>
-      <c r="E106" s="19" t="n">
-        <v>-32</v>
-      </c>
+      <c r="E106" s="19" t="n"/>
       <c r="F106" s="1" t="n"/>
       <c r="G106" s="1" t="n"/>
       <c r="H106" s="1" t="n"/>
@@ -3582,13 +3498,9 @@
           <t>Protein Bar x 50 gr frutilla y yogurt</t>
         </is>
       </c>
-      <c r="C107" s="20" t="n">
-        <v>-74</v>
-      </c>
+      <c r="C107" s="20" t="n"/>
       <c r="D107" s="20" t="n"/>
-      <c r="E107" s="19" t="n">
-        <v>-74</v>
-      </c>
+      <c r="E107" s="19" t="n"/>
       <c r="F107" s="1" t="n"/>
       <c r="G107" s="1" t="n"/>
       <c r="H107" s="1" t="n"/>
@@ -3761,13 +3673,9 @@
           <t>DUBAI BAR</t>
         </is>
       </c>
-      <c r="C114" s="18" t="n">
-        <v>-49</v>
-      </c>
+      <c r="C114" s="18" t="n"/>
       <c r="D114" s="18" t="n"/>
-      <c r="E114" s="19" t="n">
-        <v>-49</v>
-      </c>
+      <c r="E114" s="19" t="n"/>
       <c r="F114" s="1" t="n"/>
       <c r="G114" s="1" t="n"/>
       <c r="H114" s="1" t="n"/>
@@ -3838,13 +3746,9 @@
           <t>ENERGY GEL FRUTOS ROJOS ULTRA TECH CAJA X 12 UNIDADES</t>
         </is>
       </c>
-      <c r="C117" s="20" t="n">
-        <v>-15</v>
-      </c>
+      <c r="C117" s="20" t="n"/>
       <c r="D117" s="20" t="n"/>
-      <c r="E117" s="19" t="n">
-        <v>-15</v>
-      </c>
+      <c r="E117" s="19" t="n"/>
       <c r="F117" s="1" t="n"/>
       <c r="G117" s="1" t="n"/>
       <c r="H117" s="1" t="n"/>
@@ -3892,13 +3796,9 @@
           <t>Energy Gel con Cafeína x 32 g - Sabor árandano x 12 unidades</t>
         </is>
       </c>
-      <c r="C119" s="18" t="n">
-        <v>-2</v>
-      </c>
+      <c r="C119" s="18" t="n"/>
       <c r="D119" s="18" t="n"/>
-      <c r="E119" s="19" t="n">
-        <v>-2</v>
-      </c>
+      <c r="E119" s="19" t="n"/>
       <c r="F119" s="1" t="n"/>
       <c r="G119" s="1" t="n"/>
       <c r="H119" s="1" t="n"/>
@@ -4517,13 +4417,9 @@
           <t>VASO TAPA A ROSCA ULTRA TECH</t>
         </is>
       </c>
-      <c r="C144" s="20" t="n">
-        <v>-18</v>
-      </c>
+      <c r="C144" s="20" t="n"/>
       <c r="D144" s="20" t="n"/>
-      <c r="E144" s="19" t="n">
-        <v>-18</v>
-      </c>
+      <c r="E144" s="19" t="n"/>
       <c r="F144" s="1" t="n"/>
       <c r="G144" s="1" t="n"/>
       <c r="H144" s="1" t="n"/>
@@ -4621,13 +4517,9 @@
           <t>Shaker Eat - shaker 1</t>
         </is>
       </c>
-      <c r="C148" s="18" t="n">
-        <v>-9</v>
-      </c>
+      <c r="C148" s="18" t="n"/>
       <c r="D148" s="18" t="n"/>
-      <c r="E148" s="19" t="n">
-        <v>-9</v>
-      </c>
+      <c r="E148" s="19" t="n"/>
       <c r="F148" s="1" t="n"/>
       <c r="G148" s="1" t="n"/>
       <c r="H148" s="1" t="n"/>
@@ -4823,13 +4715,9 @@
           <t xml:space="preserve">Aceite de pescado + Hig. De Bacalao + Chia x 30 compr. </t>
         </is>
       </c>
-      <c r="C156" s="18" t="n">
-        <v>-12</v>
-      </c>
+      <c r="C156" s="18" t="n"/>
       <c r="D156" s="18" t="n"/>
-      <c r="E156" s="19" t="n">
-        <v>-12</v>
-      </c>
+      <c r="E156" s="19" t="n"/>
       <c r="F156" s="1" t="n"/>
       <c r="G156" s="1" t="n"/>
       <c r="H156" s="1" t="n"/>
@@ -4975,13 +4863,9 @@
           <t>Arginina x 30  VT</t>
         </is>
       </c>
-      <c r="C162" s="18" t="n">
-        <v>-16</v>
-      </c>
+      <c r="C162" s="18" t="n"/>
       <c r="D162" s="18" t="n"/>
-      <c r="E162" s="19" t="n">
-        <v>-16</v>
-      </c>
+      <c r="E162" s="19" t="n"/>
       <c r="F162" s="1" t="n"/>
       <c r="G162" s="1" t="n"/>
       <c r="H162" s="1" t="n"/>
@@ -5079,13 +4963,9 @@
           <t>ASHWAGANDHA 1300 MG X 60 CAPS</t>
         </is>
       </c>
-      <c r="C166" s="20" t="n">
-        <v>-45</v>
-      </c>
+      <c r="C166" s="20" t="n"/>
       <c r="D166" s="20" t="n"/>
-      <c r="E166" s="19" t="n">
-        <v>-45</v>
-      </c>
+      <c r="E166" s="19" t="n"/>
       <c r="F166" s="1" t="n"/>
       <c r="G166" s="1" t="n"/>
       <c r="H166" s="1" t="n"/>
@@ -5108,13 +4988,9 @@
           <t>BISGLICINATO DE MAGNESIO X 60 CAPS VITATECH</t>
         </is>
       </c>
-      <c r="C167" s="20" t="n">
-        <v>-126</v>
-      </c>
+      <c r="C167" s="20" t="n"/>
       <c r="D167" s="20" t="n"/>
-      <c r="E167" s="19" t="n">
-        <v>-126</v>
-      </c>
+      <c r="E167" s="19" t="n"/>
       <c r="F167" s="1" t="n"/>
       <c r="G167" s="1" t="n"/>
       <c r="H167" s="1" t="n"/>
@@ -5137,13 +5013,9 @@
           <t>BISGLICINATO DE MAGNESIO POLVO LIMON</t>
         </is>
       </c>
-      <c r="C168" s="18" t="n">
-        <v>-31</v>
-      </c>
+      <c r="C168" s="18" t="n"/>
       <c r="D168" s="18" t="n"/>
-      <c r="E168" s="19" t="n">
-        <v>-31</v>
-      </c>
+      <c r="E168" s="19" t="n"/>
       <c r="F168" s="1" t="n"/>
       <c r="G168" s="1" t="n"/>
       <c r="H168" s="1" t="n"/>
@@ -5391,13 +5263,9 @@
           <t xml:space="preserve">CITRATO DE POTASIO </t>
         </is>
       </c>
-      <c r="C178" s="18" t="n">
-        <v>-11</v>
-      </c>
+      <c r="C178" s="18" t="n"/>
       <c r="D178" s="18" t="n"/>
-      <c r="E178" s="19" t="n">
-        <v>-11</v>
-      </c>
+      <c r="E178" s="19" t="n"/>
       <c r="F178" s="1" t="n"/>
       <c r="G178" s="1" t="n"/>
       <c r="H178" s="1" t="n"/>
@@ -5495,13 +5363,9 @@
           <t>Colageno x 60 compr VT</t>
         </is>
       </c>
-      <c r="C182" s="20" t="n">
-        <v>-20</v>
-      </c>
+      <c r="C182" s="20" t="n"/>
       <c r="D182" s="20" t="n"/>
-      <c r="E182" s="19" t="n">
-        <v>-20</v>
-      </c>
+      <c r="E182" s="19" t="n"/>
       <c r="F182" s="1" t="n"/>
       <c r="G182" s="1" t="n"/>
       <c r="H182" s="1" t="n"/>
@@ -5599,13 +5463,9 @@
           <t>COLAGENO DEFENSE</t>
         </is>
       </c>
-      <c r="C186" s="18" t="n">
-        <v>-9</v>
-      </c>
+      <c r="C186" s="18" t="n"/>
       <c r="D186" s="18" t="n"/>
-      <c r="E186" s="19" t="n">
-        <v>-9</v>
-      </c>
+      <c r="E186" s="19" t="n"/>
       <c r="F186" s="1" t="n"/>
       <c r="G186" s="1" t="n"/>
       <c r="H186" s="1" t="n"/>
@@ -5628,13 +5488,9 @@
           <t>PROTEINA DE COLAGENO X 360 GR VITATECH FRUTOS DEL BOSQUE</t>
         </is>
       </c>
-      <c r="C187" s="20" t="n">
-        <v>-26</v>
-      </c>
+      <c r="C187" s="20" t="n"/>
       <c r="D187" s="20" t="n"/>
-      <c r="E187" s="19" t="n">
-        <v>-26</v>
-      </c>
+      <c r="E187" s="19" t="n"/>
       <c r="F187" s="1" t="n"/>
       <c r="G187" s="1" t="n"/>
       <c r="H187" s="1" t="n"/>
@@ -5707,13 +5563,9 @@
           <t>VITAFLEX X 360 GR VITATECH</t>
         </is>
       </c>
-      <c r="C190" s="20" t="n">
-        <v>-95</v>
-      </c>
+      <c r="C190" s="20" t="n"/>
       <c r="D190" s="20" t="n"/>
-      <c r="E190" s="19" t="n">
-        <v>-95</v>
-      </c>
+      <c r="E190" s="19" t="n"/>
       <c r="F190" s="1" t="n"/>
       <c r="G190" s="1" t="n"/>
       <c r="H190" s="1" t="n"/>
@@ -5736,13 +5588,9 @@
           <t>Complejo B x 60 comprimidos VT</t>
         </is>
       </c>
-      <c r="C191" s="20" t="n">
-        <v>-25</v>
-      </c>
+      <c r="C191" s="20" t="n"/>
       <c r="D191" s="20" t="n"/>
-      <c r="E191" s="19" t="n">
-        <v>-25</v>
-      </c>
+      <c r="E191" s="19" t="n"/>
       <c r="F191" s="1" t="n"/>
       <c r="G191" s="1" t="n"/>
       <c r="H191" s="1" t="n"/>
@@ -5865,13 +5713,9 @@
           <t>CURCUMA + PIMIENTA NEGRA Y VITAMINA E X30 CAPS</t>
         </is>
       </c>
-      <c r="C196" s="18" t="n">
-        <v>-20</v>
-      </c>
+      <c r="C196" s="18" t="n"/>
       <c r="D196" s="18" t="n"/>
-      <c r="E196" s="19" t="n">
-        <v>-20</v>
-      </c>
+      <c r="E196" s="19" t="n"/>
       <c r="F196" s="1" t="n"/>
       <c r="G196" s="1" t="n"/>
       <c r="H196" s="1" t="n"/>
@@ -5969,13 +5813,9 @@
           <t>GLUTATION * 30 CAPS</t>
         </is>
       </c>
-      <c r="C200" s="18" t="n">
-        <v>-1</v>
-      </c>
+      <c r="C200" s="18" t="n"/>
       <c r="D200" s="18" t="n"/>
-      <c r="E200" s="19" t="n">
-        <v>-1</v>
-      </c>
+      <c r="E200" s="19" t="n"/>
       <c r="F200" s="1" t="n"/>
       <c r="G200" s="1" t="n"/>
       <c r="H200" s="1" t="n"/>
@@ -6048,13 +5888,9 @@
           <t>Guarana x 60 comp VT</t>
         </is>
       </c>
-      <c r="C203" s="18" t="n">
-        <v>-13</v>
-      </c>
+      <c r="C203" s="18" t="n"/>
       <c r="D203" s="18" t="n"/>
-      <c r="E203" s="19" t="n">
-        <v>-13</v>
-      </c>
+      <c r="E203" s="19" t="n"/>
       <c r="F203" s="1" t="n"/>
       <c r="G203" s="1" t="n"/>
       <c r="H203" s="1" t="n"/>
@@ -6127,13 +5963,9 @@
           <t>Krill   VT</t>
         </is>
       </c>
-      <c r="C206" s="18" t="n">
-        <v>-14</v>
-      </c>
+      <c r="C206" s="18" t="n"/>
       <c r="D206" s="18" t="n"/>
-      <c r="E206" s="19" t="n">
-        <v>-14</v>
-      </c>
+      <c r="E206" s="19" t="n"/>
       <c r="F206" s="1" t="n"/>
       <c r="G206" s="1" t="n"/>
       <c r="H206" s="1" t="n"/>
@@ -6231,13 +6063,9 @@
           <t>Luteina x 30 caps VT</t>
         </is>
       </c>
-      <c r="C210" s="18" t="n">
-        <v>-13</v>
-      </c>
+      <c r="C210" s="18" t="n"/>
       <c r="D210" s="18" t="n"/>
-      <c r="E210" s="19" t="n">
-        <v>-13</v>
-      </c>
+      <c r="E210" s="19" t="n"/>
       <c r="F210" s="1" t="n"/>
       <c r="G210" s="1" t="n"/>
       <c r="H210" s="1" t="n"/>
@@ -6285,13 +6113,9 @@
           <t>MAGNESIO X 30 COMP VITATECH</t>
         </is>
       </c>
-      <c r="C212" s="20" t="n">
-        <v>-14</v>
-      </c>
+      <c r="C212" s="20" t="n"/>
       <c r="D212" s="20" t="n"/>
-      <c r="E212" s="19" t="n">
-        <v>-14</v>
-      </c>
+      <c r="E212" s="19" t="n"/>
       <c r="F212" s="1" t="n"/>
       <c r="G212" s="1" t="n"/>
       <c r="H212" s="1" t="n"/>
@@ -6339,13 +6163,9 @@
           <t>VITATECH CITRATO DE MAGNESIO X 30 CÁPSULAS</t>
         </is>
       </c>
-      <c r="C214" s="20" t="n">
-        <v>-87</v>
-      </c>
+      <c r="C214" s="20" t="n"/>
       <c r="D214" s="20" t="n"/>
-      <c r="E214" s="19" t="n">
-        <v>-87</v>
-      </c>
+      <c r="E214" s="19" t="n"/>
       <c r="F214" s="1" t="n"/>
       <c r="G214" s="1" t="n"/>
       <c r="H214" s="1" t="n"/>
@@ -6368,13 +6188,9 @@
           <t>CITRATO DE MAGNESIO  POLVO ARANDANO</t>
         </is>
       </c>
-      <c r="C215" s="20" t="n">
-        <v>-21</v>
-      </c>
+      <c r="C215" s="20" t="n"/>
       <c r="D215" s="20" t="n"/>
-      <c r="E215" s="19" t="n">
-        <v>-21</v>
-      </c>
+      <c r="E215" s="19" t="n"/>
       <c r="F215" s="1" t="n"/>
       <c r="G215" s="1" t="n"/>
       <c r="H215" s="1" t="n"/>
@@ -6422,13 +6238,9 @@
           <t>MELENA DE LEON X 60 CAPS VITATECH 1000 MG</t>
         </is>
       </c>
-      <c r="C217" s="20" t="n">
-        <v>-46</v>
-      </c>
+      <c r="C217" s="20" t="n"/>
       <c r="D217" s="20" t="n"/>
-      <c r="E217" s="19" t="n">
-        <v>-46</v>
-      </c>
+      <c r="E217" s="19" t="n"/>
       <c r="F217" s="1" t="n"/>
       <c r="G217" s="1" t="n"/>
       <c r="H217" s="1" t="n"/>
@@ -6451,13 +6263,9 @@
           <t>MULTIVITAMINAS Y MINERALES X 60 COMP VITATECH</t>
         </is>
       </c>
-      <c r="C218" s="20" t="n">
-        <v>-20</v>
-      </c>
+      <c r="C218" s="20" t="n"/>
       <c r="D218" s="20" t="n"/>
-      <c r="E218" s="19" t="n">
-        <v>-20</v>
-      </c>
+      <c r="E218" s="19" t="n"/>
       <c r="F218" s="1" t="n"/>
       <c r="G218" s="1" t="n"/>
       <c r="H218" s="1" t="n"/>
@@ -6480,13 +6288,9 @@
           <t xml:space="preserve">Plant Protein bar caja x 12 unidades </t>
         </is>
       </c>
-      <c r="C219" s="18" t="n">
-        <v>-18</v>
-      </c>
+      <c r="C219" s="18" t="n"/>
       <c r="D219" s="18" t="n"/>
-      <c r="E219" s="19" t="n">
-        <v>-18</v>
-      </c>
+      <c r="E219" s="19" t="n"/>
       <c r="F219" s="1" t="n"/>
       <c r="G219" s="1" t="n"/>
       <c r="H219" s="1" t="n"/>
@@ -6509,13 +6313,9 @@
           <t>Potasio - Magnesio x 60 caps</t>
         </is>
       </c>
-      <c r="C220" s="20" t="n">
-        <v>-59</v>
-      </c>
+      <c r="C220" s="20" t="n"/>
       <c r="D220" s="20" t="n"/>
-      <c r="E220" s="19" t="n">
-        <v>-59</v>
-      </c>
+      <c r="E220" s="19" t="n"/>
       <c r="F220" s="1" t="n"/>
       <c r="G220" s="1" t="n"/>
       <c r="H220" s="1" t="n"/>
@@ -6613,13 +6413,9 @@
           <t>RESVERATROL PLUS</t>
         </is>
       </c>
-      <c r="C224" s="18" t="n">
-        <v>-20</v>
-      </c>
+      <c r="C224" s="18" t="n"/>
       <c r="D224" s="18" t="n"/>
-      <c r="E224" s="19" t="n">
-        <v>-20</v>
-      </c>
+      <c r="E224" s="19" t="n"/>
       <c r="F224" s="1" t="n"/>
       <c r="G224" s="1" t="n"/>
       <c r="H224" s="1" t="n"/>
@@ -6767,13 +6563,9 @@
           <t>TREONATO DE MAGNESIO X 60 CAPS VITATECH</t>
         </is>
       </c>
-      <c r="C230" s="20" t="n">
-        <v>-20</v>
-      </c>
+      <c r="C230" s="20" t="n"/>
       <c r="D230" s="20" t="n"/>
-      <c r="E230" s="19" t="n">
-        <v>-20</v>
-      </c>
+      <c r="E230" s="19" t="n"/>
       <c r="F230" s="1" t="n"/>
       <c r="G230" s="1" t="n"/>
       <c r="H230" s="1" t="n"/>
@@ -6796,13 +6588,9 @@
           <t>Vision x 30 comp VT</t>
         </is>
       </c>
-      <c r="C231" s="18" t="n">
-        <v>-9</v>
-      </c>
+      <c r="C231" s="18" t="n"/>
       <c r="D231" s="18" t="n"/>
-      <c r="E231" s="19" t="n">
-        <v>-9</v>
-      </c>
+      <c r="E231" s="19" t="n"/>
       <c r="F231" s="1" t="n"/>
       <c r="G231" s="1" t="n"/>
       <c r="H231" s="1" t="n"/>
@@ -6850,13 +6638,9 @@
           <t>Vita stress x 30</t>
         </is>
       </c>
-      <c r="C233" s="18" t="n">
-        <v>-10</v>
-      </c>
+      <c r="C233" s="18" t="n"/>
       <c r="D233" s="18" t="n"/>
-      <c r="E233" s="19" t="n">
-        <v>-10</v>
-      </c>
+      <c r="E233" s="19" t="n"/>
       <c r="F233" s="1" t="n"/>
       <c r="G233" s="1" t="n"/>
       <c r="H233" s="1" t="n"/>
@@ -6879,13 +6663,9 @@
           <t>Vitamina A  x 30 comp VT</t>
         </is>
       </c>
-      <c r="C234" s="18" t="n">
-        <v>-3</v>
-      </c>
+      <c r="C234" s="18" t="n"/>
       <c r="D234" s="18" t="n"/>
-      <c r="E234" s="19" t="n">
-        <v>-3</v>
-      </c>
+      <c r="E234" s="19" t="n"/>
       <c r="F234" s="1" t="n"/>
       <c r="G234" s="1" t="n"/>
       <c r="H234" s="1" t="n"/>
@@ -6908,13 +6688,9 @@
           <t xml:space="preserve"> VITAMINA C X 30 COMP VITATECH</t>
         </is>
       </c>
-      <c r="C235" s="20" t="n">
-        <v>-9</v>
-      </c>
+      <c r="C235" s="20" t="n"/>
       <c r="D235" s="20" t="n"/>
-      <c r="E235" s="19" t="n">
-        <v>-9</v>
-      </c>
+      <c r="E235" s="19" t="n"/>
       <c r="F235" s="1" t="n"/>
       <c r="G235" s="1" t="n"/>
       <c r="H235" s="1" t="n"/>
@@ -7037,13 +6813,9 @@
           <t>ZINC X 30 COMP VITATECH</t>
         </is>
       </c>
-      <c r="C240" s="20" t="n">
-        <v>-82</v>
-      </c>
+      <c r="C240" s="20" t="n"/>
       <c r="D240" s="20" t="n"/>
-      <c r="E240" s="19" t="n">
-        <v>-82</v>
-      </c>
+      <c r="E240" s="19" t="n"/>
       <c r="F240" s="1" t="n"/>
       <c r="G240" s="1" t="n"/>
       <c r="H240" s="1" t="n"/>
@@ -7066,13 +6838,9 @@
           <t>ZINC QUELATO</t>
         </is>
       </c>
-      <c r="C241" s="18" t="n">
-        <v>-6</v>
-      </c>
+      <c r="C241" s="18" t="n"/>
       <c r="D241" s="18" t="n"/>
-      <c r="E241" s="19" t="n">
-        <v>-6</v>
-      </c>
+      <c r="E241" s="19" t="n"/>
       <c r="F241" s="1" t="n"/>
       <c r="G241" s="1" t="n"/>
       <c r="H241" s="1" t="n"/>
@@ -7095,13 +6863,9 @@
           <t>VITAMINA K2 X 30 COMP VITATECH</t>
         </is>
       </c>
-      <c r="C242" s="20" t="n">
-        <v>-61</v>
-      </c>
+      <c r="C242" s="20" t="n"/>
       <c r="D242" s="20" t="n"/>
-      <c r="E242" s="19" t="n">
-        <v>-61</v>
-      </c>
+      <c r="E242" s="19" t="n"/>
       <c r="F242" s="1" t="n"/>
       <c r="G242" s="1" t="n"/>
       <c r="H242" s="1" t="n"/>
@@ -7174,13 +6938,9 @@
           <t>NAD+ VITATECH X 60 CAPSULAS</t>
         </is>
       </c>
-      <c r="C245" s="20" t="n">
-        <v>-142</v>
-      </c>
+      <c r="C245" s="20" t="n"/>
       <c r="D245" s="20" t="n"/>
-      <c r="E245" s="19" t="n">
-        <v>-142</v>
-      </c>
+      <c r="E245" s="19" t="n"/>
       <c r="F245" s="1" t="n"/>
       <c r="G245" s="1" t="n"/>
       <c r="H245" s="1" t="n"/>
@@ -7203,13 +6963,9 @@
           <t>NAD+ TESTO HOMBRE</t>
         </is>
       </c>
-      <c r="C246" s="20" t="n">
-        <v>-34</v>
-      </c>
+      <c r="C246" s="20" t="n"/>
       <c r="D246" s="20" t="n"/>
-      <c r="E246" s="19" t="n">
-        <v>-34</v>
-      </c>
+      <c r="E246" s="19" t="n"/>
       <c r="F246" s="1" t="n"/>
       <c r="G246" s="1" t="n"/>
       <c r="H246" s="1" t="n"/>
@@ -7232,13 +6988,9 @@
           <t>NAD EN POLVO X 348 GRS</t>
         </is>
       </c>
-      <c r="C247" s="18" t="n">
-        <v>-61</v>
-      </c>
+      <c r="C247" s="18" t="n"/>
       <c r="D247" s="18" t="n"/>
-      <c r="E247" s="19" t="n">
-        <v>-61</v>
-      </c>
+      <c r="E247" s="19" t="n"/>
       <c r="F247" s="1" t="n"/>
       <c r="G247" s="1" t="n"/>
       <c r="H247" s="1" t="n"/>
@@ -7530,13 +7282,9 @@
           <t>Protein Bar Mini 25 gr x 24 unidades</t>
         </is>
       </c>
-      <c r="C259" s="18" t="n">
-        <v>-15</v>
-      </c>
+      <c r="C259" s="18" t="n"/>
       <c r="D259" s="18" t="n"/>
-      <c r="E259" s="19" t="n">
-        <v>-15</v>
-      </c>
+      <c r="E259" s="19" t="n"/>
       <c r="F259" s="1" t="n"/>
       <c r="G259" s="1" t="n"/>
       <c r="H259" s="1" t="n"/>
@@ -7559,13 +7307,9 @@
           <t>PROTEIN BAR SUGAR FREE X 12 UNIDADES PROTEIN FACTORY DULCE DE LECHE</t>
         </is>
       </c>
-      <c r="C260" s="20" t="n">
-        <v>-222</v>
-      </c>
+      <c r="C260" s="20" t="n"/>
       <c r="D260" s="20" t="n"/>
-      <c r="E260" s="19" t="n">
-        <v>-222</v>
-      </c>
+      <c r="E260" s="19" t="n"/>
       <c r="F260" s="1" t="n"/>
       <c r="G260" s="1" t="n"/>
       <c r="H260" s="1" t="n"/>
@@ -7588,13 +7332,9 @@
           <t>Protein Bar Sugar Free x 46 gr Chocolate</t>
         </is>
       </c>
-      <c r="C261" s="18" t="n">
-        <v>-58</v>
-      </c>
+      <c r="C261" s="18" t="n"/>
       <c r="D261" s="18" t="n"/>
-      <c r="E261" s="19" t="n">
-        <v>-58</v>
-      </c>
+      <c r="E261" s="19" t="n"/>
       <c r="F261" s="1" t="n"/>
       <c r="G261" s="1" t="n"/>
       <c r="H261" s="1" t="n"/>
@@ -7640,13 +7380,9 @@
           <t>PROTEIN PANCAKE DOYPACK PROTEIN FACTORY</t>
         </is>
       </c>
-      <c r="C263" s="20" t="n">
-        <v>-55</v>
-      </c>
+      <c r="C263" s="20" t="n"/>
       <c r="D263" s="20" t="n"/>
-      <c r="E263" s="19" t="n">
-        <v>-55</v>
-      </c>
+      <c r="E263" s="19" t="n"/>
       <c r="F263" s="1" t="n"/>
       <c r="G263" s="1" t="n"/>
       <c r="H263" s="1" t="n"/>
@@ -7694,13 +7430,9 @@
           <t xml:space="preserve">Protein Cafe Latte x 240 grs </t>
         </is>
       </c>
-      <c r="C265" s="18" t="n">
-        <v>-33</v>
-      </c>
+      <c r="C265" s="18" t="n"/>
       <c r="D265" s="18" t="n"/>
-      <c r="E265" s="19" t="n">
-        <v>-33</v>
-      </c>
+      <c r="E265" s="19" t="n"/>
       <c r="F265" s="1" t="n"/>
       <c r="G265" s="1" t="n"/>
       <c r="H265" s="1" t="n"/>
@@ -7723,13 +7455,9 @@
           <t xml:space="preserve">Protein Omelette x 240 grs </t>
         </is>
       </c>
-      <c r="C266" s="20" t="n">
-        <v>-9</v>
-      </c>
+      <c r="C266" s="20" t="n"/>
       <c r="D266" s="20" t="n"/>
-      <c r="E266" s="19" t="n">
-        <v>-9</v>
-      </c>
+      <c r="E266" s="19" t="n"/>
       <c r="F266" s="1" t="n"/>
       <c r="G266" s="1" t="n"/>
       <c r="H266" s="1" t="n"/>
@@ -7825,13 +7553,9 @@
           <t>Xing Yu x 4 caps</t>
         </is>
       </c>
-      <c r="C270" s="18" t="n">
-        <v>-130</v>
-      </c>
+      <c r="C270" s="18" t="n"/>
       <c r="D270" s="18" t="n"/>
-      <c r="E270" s="19" t="n">
-        <v>-130</v>
-      </c>
+      <c r="E270" s="19" t="n"/>
       <c r="F270" s="1" t="n"/>
       <c r="G270" s="1" t="n"/>
       <c r="H270" s="1" t="n"/>
@@ -7854,13 +7578,9 @@
           <t>Xing Yu x 8 caps</t>
         </is>
       </c>
-      <c r="C271" s="18" t="n">
-        <v>-36</v>
-      </c>
+      <c r="C271" s="18" t="n"/>
       <c r="D271" s="18" t="n"/>
-      <c r="E271" s="19" t="n">
-        <v>-36</v>
-      </c>
+      <c r="E271" s="19" t="n"/>
       <c r="F271" s="1" t="n"/>
       <c r="G271" s="1" t="n"/>
       <c r="H271" s="1" t="n"/>
@@ -7883,13 +7603,9 @@
           <t>ULTRA MUJER</t>
         </is>
       </c>
-      <c r="C272" s="35" t="n">
-        <v>-207</v>
-      </c>
+      <c r="C272" s="35" t="n"/>
       <c r="D272" s="35" t="n"/>
-      <c r="E272" s="19" t="n">
-        <v>-207</v>
-      </c>
+      <c r="E272" s="19" t="n"/>
       <c r="F272" s="1" t="n"/>
       <c r="G272" s="1" t="n"/>
       <c r="H272" s="1" t="n"/>
@@ -7912,13 +7628,9 @@
           <t>ULTRA HOMBRE</t>
         </is>
       </c>
-      <c r="C273" s="35" t="n">
-        <v>-40</v>
-      </c>
+      <c r="C273" s="35" t="n"/>
       <c r="D273" s="35" t="n"/>
-      <c r="E273" s="19" t="n">
-        <v>-40</v>
-      </c>
+      <c r="E273" s="19" t="n"/>
       <c r="F273" s="1" t="n"/>
       <c r="G273" s="1" t="n"/>
       <c r="H273" s="1" t="n"/>
@@ -8394,13 +8106,9 @@
           <t>EXHIBIDOR MOSTRADOR BARRAS ULTRA TECH (DOBLE)</t>
         </is>
       </c>
-      <c r="C293" s="35" t="n">
-        <v>-3</v>
-      </c>
+      <c r="C293" s="35" t="n"/>
       <c r="D293" s="35" t="n"/>
-      <c r="E293" s="19" t="n">
-        <v>-3</v>
-      </c>
+      <c r="E293" s="19" t="n"/>
       <c r="F293" s="1" t="n"/>
       <c r="G293" s="1" t="n"/>
       <c r="H293" s="1" t="n"/>
@@ -8483,13 +8191,9 @@
           <t>FOLLETOS ULTRA TECH - PACK X 15 FOLLETOS</t>
         </is>
       </c>
-      <c r="C296" s="38" t="n">
-        <v>-12</v>
-      </c>
+      <c r="C296" s="38" t="n"/>
       <c r="D296" s="38" t="n"/>
-      <c r="E296" s="19" t="n">
-        <v>-12</v>
-      </c>
+      <c r="E296" s="19" t="n"/>
       <c r="F296" s="1" t="n"/>
       <c r="G296" s="1" t="n"/>
       <c r="H296" s="1" t="n"/>
@@ -8522,13 +8226,9 @@
           <t xml:space="preserve">FOLLETOS GELES </t>
         </is>
       </c>
-      <c r="C297" s="38" t="n">
-        <v>-1</v>
-      </c>
+      <c r="C297" s="38" t="n"/>
       <c r="D297" s="38" t="n"/>
-      <c r="E297" s="19" t="n">
-        <v>-1</v>
-      </c>
+      <c r="E297" s="19" t="n"/>
       <c r="F297" s="1" t="n"/>
       <c r="G297" s="1" t="n"/>
       <c r="H297" s="1" t="n"/>
@@ -8904,13 +8604,9 @@
           <t>FOLLETOS VITATECH - PACK X 15 FOLLETOS</t>
         </is>
       </c>
-      <c r="C311" s="38" t="n">
-        <v>-15</v>
-      </c>
+      <c r="C311" s="38" t="n"/>
       <c r="D311" s="38" t="n"/>
-      <c r="E311" s="19" t="n">
-        <v>-15</v>
-      </c>
+      <c r="E311" s="19" t="n"/>
       <c r="F311" s="1" t="n"/>
       <c r="G311" s="1" t="n"/>
       <c r="H311" s="1" t="n"/>
@@ -9424,13 +9120,9 @@
           <t>DUBAI protein bar x unidad</t>
         </is>
       </c>
-      <c r="C333" s="35" t="n">
-        <v>-15</v>
-      </c>
+      <c r="C333" s="35" t="n"/>
       <c r="D333" s="35" t="n"/>
-      <c r="E333" s="19" t="n">
-        <v>-15</v>
-      </c>
+      <c r="E333" s="19" t="n"/>
       <c r="F333" s="1" t="n"/>
       <c r="G333" s="1" t="n"/>
       <c r="H333" s="1" t="n"/>
@@ -9478,13 +9170,9 @@
           <t>Protein Bar - 50 g banana x unidad</t>
         </is>
       </c>
-      <c r="C335" s="35" t="n">
-        <v>-2</v>
-      </c>
+      <c r="C335" s="35" t="n"/>
       <c r="D335" s="35" t="n"/>
-      <c r="E335" s="19" t="n">
-        <v>-2</v>
-      </c>
+      <c r="E335" s="19" t="n"/>
       <c r="F335" s="1" t="n"/>
       <c r="G335" s="1" t="n"/>
       <c r="H335" s="1" t="n"/>
@@ -9507,13 +9195,9 @@
           <t>Protein Bar - 50 g frutilla con yogurt x unidad</t>
         </is>
       </c>
-      <c r="C336" s="35" t="n">
-        <v>-2</v>
-      </c>
+      <c r="C336" s="35" t="n"/>
       <c r="D336" s="35" t="n"/>
-      <c r="E336" s="19" t="n">
-        <v>-2</v>
-      </c>
+      <c r="E336" s="19" t="n"/>
       <c r="F336" s="1" t="n"/>
       <c r="G336" s="1" t="n"/>
       <c r="H336" s="1" t="n"/>
@@ -10086,13 +9770,9 @@
           <t>Protein Bar - 50 g banana x unidad</t>
         </is>
       </c>
-      <c r="C359" s="35" t="n">
-        <v>-2</v>
-      </c>
+      <c r="C359" s="35" t="n"/>
       <c r="D359" s="35" t="n"/>
-      <c r="E359" s="19" t="n">
-        <v>-2</v>
-      </c>
+      <c r="E359" s="19" t="n"/>
       <c r="F359" s="1" t="n"/>
       <c r="G359" s="1" t="n"/>
       <c r="H359" s="1" t="n"/>
@@ -10115,13 +9795,9 @@
           <t>Protein Bar - 50 g frutilla con yogurt x unidad</t>
         </is>
       </c>
-      <c r="C360" s="35" t="n">
-        <v>-2</v>
-      </c>
+      <c r="C360" s="35" t="n"/>
       <c r="D360" s="35" t="n"/>
-      <c r="E360" s="19" t="n">
-        <v>-2</v>
-      </c>
+      <c r="E360" s="19" t="n"/>
       <c r="F360" s="1" t="n"/>
       <c r="G360" s="1" t="n"/>
       <c r="H360" s="1" t="n"/>
@@ -10144,13 +9820,9 @@
           <t>Protein bar café x unidad</t>
         </is>
       </c>
-      <c r="C361" s="35" t="n">
-        <v>-2</v>
-      </c>
+      <c r="C361" s="35" t="n"/>
       <c r="D361" s="35" t="n"/>
-      <c r="E361" s="19" t="n">
-        <v>-2</v>
-      </c>
+      <c r="E361" s="19" t="n"/>
       <c r="F361" s="1" t="n"/>
       <c r="G361" s="1" t="n"/>
       <c r="H361" s="1" t="n"/>
@@ -10223,13 +9895,9 @@
           <t>DUBAI protein bar x unidad</t>
         </is>
       </c>
-      <c r="C364" s="35" t="n">
-        <v>-15</v>
-      </c>
+      <c r="C364" s="35" t="n"/>
       <c r="D364" s="35" t="n"/>
-      <c r="E364" s="19" t="n">
-        <v>-15</v>
-      </c>
+      <c r="E364" s="19" t="n"/>
       <c r="F364" s="1" t="n"/>
       <c r="G364" s="1" t="n"/>
       <c r="H364" s="1" t="n"/>
@@ -10277,13 +9945,9 @@
           <t>Protein Bar - 50 g banana x unidad</t>
         </is>
       </c>
-      <c r="C366" s="35" t="n">
-        <v>-2</v>
-      </c>
+      <c r="C366" s="35" t="n"/>
       <c r="D366" s="35" t="n"/>
-      <c r="E366" s="19" t="n">
-        <v>-2</v>
-      </c>
+      <c r="E366" s="19" t="n"/>
       <c r="F366" s="1" t="n"/>
       <c r="G366" s="1" t="n"/>
       <c r="H366" s="1" t="n"/>
@@ -10306,13 +9970,9 @@
           <t>Protein Bar - 50 g frutilla con yogurt x unidad</t>
         </is>
       </c>
-      <c r="C367" s="35" t="n">
-        <v>-2</v>
-      </c>
+      <c r="C367" s="35" t="n"/>
       <c r="D367" s="35" t="n"/>
-      <c r="E367" s="19" t="n">
-        <v>-2</v>
-      </c>
+      <c r="E367" s="19" t="n"/>
       <c r="F367" s="1" t="n"/>
       <c r="G367" s="1" t="n"/>
       <c r="H367" s="1" t="n"/>
@@ -10335,13 +9995,9 @@
           <t>Protein bar café x unidad</t>
         </is>
       </c>
-      <c r="C368" s="35" t="n">
-        <v>-2</v>
-      </c>
+      <c r="C368" s="35" t="n"/>
       <c r="D368" s="35" t="n"/>
-      <c r="E368" s="19" t="n">
-        <v>-2</v>
-      </c>
+      <c r="E368" s="19" t="n"/>
       <c r="F368" s="1" t="n"/>
       <c r="G368" s="1" t="n"/>
       <c r="H368" s="1" t="n"/>
